--- a/output/yearly_population_iteration_80_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_80_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5181</v>
+        <v>4788</v>
       </c>
       <c r="C2" t="n">
-        <v>11667</v>
+        <v>14581</v>
       </c>
       <c r="D2" t="n">
-        <v>25550</v>
+        <v>28254</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3406</v>
+        <v>3188</v>
       </c>
       <c r="C3" t="n">
-        <v>5369</v>
+        <v>8569</v>
       </c>
       <c r="D3" t="n">
-        <v>15785</v>
+        <v>15896</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2754</v>
+        <v>2405</v>
       </c>
       <c r="C4" t="n">
-        <v>7955</v>
+        <v>7262</v>
       </c>
       <c r="D4" t="n">
-        <v>6593</v>
+        <v>8162</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1798</v>
+        <v>1640</v>
       </c>
       <c r="C5" t="n">
-        <v>7030</v>
+        <v>5654</v>
       </c>
       <c r="D5" t="n">
-        <v>2176</v>
+        <v>3182</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1059</v>
+        <v>985</v>
       </c>
       <c r="C6" t="n">
-        <v>4266</v>
+        <v>3482</v>
       </c>
       <c r="D6" t="n">
-        <v>991</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>510</v>
+        <v>480</v>
       </c>
       <c r="C7" t="n">
-        <v>2170</v>
+        <v>1945</v>
       </c>
       <c r="D7" t="n">
-        <v>617</v>
+        <v>662</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="C8" t="n">
-        <v>898</v>
+        <v>925</v>
       </c>
       <c r="D8" t="n">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C9" t="n">
-        <v>352</v>
+        <v>387</v>
       </c>
       <c r="D9" t="n">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C10" t="n">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="D10" t="n">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="11">
@@ -906,10 +906,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D11" t="n">
         <v>203</v>
@@ -937,10 +937,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -962,13 +962,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D15" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -1049,10 +1049,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7320</v>
+        <v>5545</v>
       </c>
       <c r="C2" t="n">
-        <v>12984</v>
+        <v>9621</v>
       </c>
       <c r="D2" t="n">
-        <v>21724</v>
+        <v>28471</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3386</v>
+        <v>3161</v>
       </c>
       <c r="C3" t="n">
-        <v>7118</v>
+        <v>9876</v>
       </c>
       <c r="D3" t="n">
-        <v>15999</v>
+        <v>16435</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2586</v>
+        <v>2356</v>
       </c>
       <c r="C4" t="n">
-        <v>6546</v>
+        <v>7713</v>
       </c>
       <c r="D4" t="n">
-        <v>7741</v>
+        <v>9023</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1938</v>
+        <v>1733</v>
       </c>
       <c r="C5" t="n">
-        <v>7292</v>
+        <v>6192</v>
       </c>
       <c r="D5" t="n">
-        <v>2788</v>
+        <v>3850</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1240</v>
+        <v>1143</v>
       </c>
       <c r="C6" t="n">
-        <v>5352</v>
+        <v>4387</v>
       </c>
       <c r="D6" t="n">
-        <v>1138</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>663</v>
+        <v>615</v>
       </c>
       <c r="C7" t="n">
-        <v>3031</v>
+        <v>2572</v>
       </c>
       <c r="D7" t="n">
-        <v>665</v>
+        <v>744</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>277</v>
+        <v>266</v>
       </c>
       <c r="C8" t="n">
-        <v>1421</v>
+        <v>1344</v>
       </c>
       <c r="D8" t="n">
-        <v>448</v>
+        <v>453</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C9" t="n">
-        <v>562</v>
+        <v>593</v>
       </c>
       <c r="D9" t="n">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C10" t="n">
-        <v>265</v>
+        <v>278</v>
       </c>
       <c r="D10" t="n">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="11">
@@ -1217,10 +1217,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D11" t="n">
         <v>206</v>
@@ -1234,7 +1234,7 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D12" t="n">
         <v>161</v>
@@ -1248,10 +1248,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D13" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14">
@@ -1262,10 +1262,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -1273,13 +1273,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D15" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -1287,7 +1287,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C16" t="n">
         <v>49</v>
@@ -1304,7 +1304,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1318,7 +1318,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -1360,10 +1360,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8219</v>
+        <v>6707</v>
       </c>
       <c r="C2" t="n">
-        <v>11694</v>
+        <v>15694</v>
       </c>
       <c r="D2" t="n">
-        <v>24389</v>
+        <v>25578</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3983</v>
+        <v>3320</v>
       </c>
       <c r="C3" t="n">
-        <v>8361</v>
+        <v>8713</v>
       </c>
       <c r="D3" t="n">
-        <v>15662</v>
+        <v>16827</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2463</v>
+        <v>2274</v>
       </c>
       <c r="C4" t="n">
-        <v>6645</v>
+        <v>8371</v>
       </c>
       <c r="D4" t="n">
-        <v>8694</v>
+        <v>9816</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1948</v>
+        <v>1775</v>
       </c>
       <c r="C5" t="n">
-        <v>6776</v>
+        <v>6676</v>
       </c>
       <c r="D5" t="n">
-        <v>3342</v>
+        <v>4391</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1370</v>
+        <v>1246</v>
       </c>
       <c r="C6" t="n">
-        <v>5999</v>
+        <v>5000</v>
       </c>
       <c r="D6" t="n">
-        <v>1344</v>
+        <v>1809</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>789</v>
+        <v>730</v>
       </c>
       <c r="C7" t="n">
-        <v>3916</v>
+        <v>3239</v>
       </c>
       <c r="D7" t="n">
-        <v>711</v>
+        <v>827</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>369</v>
+        <v>348</v>
       </c>
       <c r="C8" t="n">
-        <v>1990</v>
+        <v>1800</v>
       </c>
       <c r="D8" t="n">
-        <v>471</v>
+        <v>485</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="C9" t="n">
-        <v>859</v>
+        <v>851</v>
       </c>
       <c r="D9" t="n">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="10">
@@ -1514,10 +1514,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C10" t="n">
-        <v>364</v>
+        <v>383</v>
       </c>
       <c r="D10" t="n">
         <v>252</v>
@@ -1528,10 +1528,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C11" t="n">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="D11" t="n">
         <v>206</v>
@@ -1545,10 +1545,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13">
@@ -1559,10 +1559,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D13" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14">
@@ -1573,10 +1573,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C15" t="n">
         <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -1598,7 +1598,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C16" t="n">
         <v>52</v>
@@ -1612,7 +1612,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C17" t="n">
         <v>41</v>
@@ -1629,7 +1629,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -1671,10 +1671,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7533</v>
+        <v>6164</v>
       </c>
       <c r="C2" t="n">
-        <v>8232</v>
+        <v>11048</v>
       </c>
       <c r="D2" t="n">
-        <v>20413</v>
+        <v>21270</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4541</v>
+        <v>3974</v>
       </c>
       <c r="C3" t="n">
-        <v>12019</v>
+        <v>13487</v>
       </c>
       <c r="D3" t="n">
-        <v>16887</v>
+        <v>18455</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1799</v>
+        <v>1640</v>
       </c>
       <c r="C4" t="n">
-        <v>10013</v>
+        <v>10828</v>
       </c>
       <c r="D4" t="n">
-        <v>7934</v>
+        <v>9390</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1265</v>
+        <v>1151</v>
       </c>
       <c r="C5" t="n">
-        <v>5879</v>
+        <v>4900</v>
       </c>
       <c r="D5" t="n">
-        <v>2183</v>
+        <v>2910</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>729</v>
+        <v>674</v>
       </c>
       <c r="C6" t="n">
-        <v>3837</v>
+        <v>3174</v>
       </c>
       <c r="D6" t="n">
-        <v>696</v>
+        <v>810</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>340</v>
+        <v>321</v>
       </c>
       <c r="C7" t="n">
-        <v>1950</v>
+        <v>1764</v>
       </c>
       <c r="D7" t="n">
-        <v>461</v>
+        <v>475</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="C8" t="n">
-        <v>841</v>
+        <v>833</v>
       </c>
       <c r="D8" t="n">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="9">
@@ -1811,10 +1811,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C9" t="n">
-        <v>356</v>
+        <v>375</v>
       </c>
       <c r="D9" t="n">
         <v>246</v>
@@ -1825,10 +1825,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C10" t="n">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="D10" t="n">
         <v>201</v>
@@ -1842,10 +1842,10 @@
         <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D11" t="n">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="12">
@@ -1856,10 +1856,10 @@
         <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D12" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="13">
@@ -1870,10 +1870,10 @@
         <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D13" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
         <v>66</v>
       </c>
       <c r="D14" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15">
@@ -1895,7 +1895,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
         <v>50</v>
@@ -1909,7 +1909,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C16" t="n">
         <v>40</v>
@@ -1926,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D17" t="n">
         <v>38</v>
@@ -1968,10 +1968,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4532</v>
+        <v>3782</v>
       </c>
       <c r="C2" t="n">
-        <v>5381</v>
+        <v>4947</v>
       </c>
       <c r="D2" t="n">
-        <v>14104</v>
+        <v>14523</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4981</v>
+        <v>4191</v>
       </c>
       <c r="C3" t="n">
-        <v>9457</v>
+        <v>11322</v>
       </c>
       <c r="D3" t="n">
-        <v>16392</v>
+        <v>17781</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2418</v>
+        <v>2193</v>
       </c>
       <c r="C4" t="n">
-        <v>10978</v>
+        <v>12088</v>
       </c>
       <c r="D4" t="n">
-        <v>9134</v>
+        <v>10590</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1381</v>
+        <v>1257</v>
       </c>
       <c r="C5" t="n">
-        <v>7666</v>
+        <v>7366</v>
       </c>
       <c r="D5" t="n">
-        <v>2821</v>
+        <v>3623</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>854</v>
+        <v>788</v>
       </c>
       <c r="C6" t="n">
-        <v>4701</v>
+        <v>3901</v>
       </c>
       <c r="D6" t="n">
-        <v>836</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>316</v>
+        <v>298</v>
       </c>
       <c r="C7" t="n">
-        <v>2602</v>
+        <v>2278</v>
       </c>
       <c r="D7" t="n">
-        <v>501</v>
+        <v>517</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="C8" t="n">
-        <v>1125</v>
+        <v>1092</v>
       </c>
       <c r="D8" t="n">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="9">
@@ -2122,10 +2122,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C9" t="n">
-        <v>393</v>
+        <v>411</v>
       </c>
       <c r="D9" t="n">
         <v>257</v>
@@ -2139,10 +2139,10 @@
         <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="D10" t="n">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="11">
@@ -2153,7 +2153,7 @@
         <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D11" t="n">
         <v>165</v>
@@ -2170,7 +2170,7 @@
         <v>92</v>
       </c>
       <c r="D12" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
         <v>64</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -2192,7 +2192,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C14" t="n">
         <v>49</v>
@@ -2223,7 +2223,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D16" t="n">
         <v>37</v>
@@ -2265,10 +2265,10 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4429</v>
+        <v>3378</v>
       </c>
       <c r="C2" t="n">
-        <v>11723</v>
+        <v>9692</v>
       </c>
       <c r="D2" t="n">
-        <v>12912</v>
+        <v>16978</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4075</v>
+        <v>3418</v>
       </c>
       <c r="C3" t="n">
-        <v>6739</v>
+        <v>7482</v>
       </c>
       <c r="D3" t="n">
-        <v>15136</v>
+        <v>16313</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2952</v>
+        <v>2569</v>
       </c>
       <c r="C4" t="n">
-        <v>10034</v>
+        <v>11476</v>
       </c>
       <c r="D4" t="n">
-        <v>9883</v>
+        <v>11270</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1604</v>
+        <v>1457</v>
       </c>
       <c r="C5" t="n">
-        <v>9074</v>
+        <v>9414</v>
       </c>
       <c r="D5" t="n">
-        <v>3704</v>
+        <v>4582</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>978</v>
+        <v>897</v>
       </c>
       <c r="C6" t="n">
-        <v>5910</v>
+        <v>5328</v>
       </c>
       <c r="D6" t="n">
-        <v>1110</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>457</v>
+        <v>426</v>
       </c>
       <c r="C7" t="n">
-        <v>3490</v>
+        <v>2967</v>
       </c>
       <c r="D7" t="n">
-        <v>541</v>
+        <v>578</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="C8" t="n">
-        <v>1700</v>
+        <v>1555</v>
       </c>
       <c r="D8" t="n">
-        <v>349</v>
+        <v>353</v>
       </c>
     </row>
     <row r="9">
@@ -2433,10 +2433,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C9" t="n">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="D9" t="n">
         <v>262</v>
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C10" t="n">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="D10" t="n">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11">
@@ -2464,7 +2464,7 @@
         <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="D11" t="n">
         <v>168</v>
@@ -2481,7 +2481,7 @@
         <v>111</v>
       </c>
       <c r="D12" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="13">
@@ -2489,13 +2489,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
         <v>71</v>
       </c>
       <c r="D13" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -2520,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D15" t="n">
         <v>48</v>
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D16" t="n">
         <v>36</v>
@@ -2562,7 +2562,7 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
         <v>13</v>
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2681</v>
+        <v>2075</v>
       </c>
       <c r="C2" t="n">
-        <v>5751</v>
+        <v>4743</v>
       </c>
       <c r="D2" t="n">
-        <v>9113</v>
+        <v>11993</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4046</v>
+        <v>3294</v>
       </c>
       <c r="C3" t="n">
-        <v>8121</v>
+        <v>7979</v>
       </c>
       <c r="D3" t="n">
-        <v>14607</v>
+        <v>16037</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3223</v>
+        <v>2805</v>
       </c>
       <c r="C4" t="n">
-        <v>9807</v>
+        <v>11150</v>
       </c>
       <c r="D4" t="n">
-        <v>10531</v>
+        <v>11943</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1680</v>
+        <v>1530</v>
       </c>
       <c r="C5" t="n">
-        <v>10743</v>
+        <v>11277</v>
       </c>
       <c r="D5" t="n">
-        <v>3805</v>
+        <v>4688</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>801</v>
+        <v>741</v>
       </c>
       <c r="C6" t="n">
-        <v>6786</v>
+        <v>6092</v>
       </c>
       <c r="D6" t="n">
-        <v>1095</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="C7" t="n">
-        <v>3405</v>
+        <v>2971</v>
       </c>
       <c r="D7" t="n">
-        <v>542</v>
+        <v>571</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C8" t="n">
-        <v>1124</v>
+        <v>1083</v>
       </c>
       <c r="D8" t="n">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>273</v>
+        <v>282</v>
       </c>
       <c r="D9" t="n">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="10">
@@ -2761,7 +2761,7 @@
         <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="D10" t="n">
         <v>164</v>
@@ -2778,7 +2778,7 @@
         <v>108</v>
       </c>
       <c r="D11" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="12">
@@ -2817,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D14" t="n">
         <v>47</v>
@@ -2831,7 +2831,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D15" t="n">
         <v>35</v>
@@ -2859,7 +2859,7 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
         <v>12</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3701</v>
+        <v>2074</v>
       </c>
       <c r="C2" t="n">
-        <v>7196</v>
+        <v>5887</v>
       </c>
       <c r="D2" t="n">
-        <v>12484</v>
+        <v>11970</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3008</v>
+        <v>2415</v>
       </c>
       <c r="C3" t="n">
-        <v>6340</v>
+        <v>5919</v>
       </c>
       <c r="D3" t="n">
-        <v>12945</v>
+        <v>14621</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3087</v>
+        <v>2639</v>
       </c>
       <c r="C4" t="n">
-        <v>8936</v>
+        <v>9517</v>
       </c>
       <c r="D4" t="n">
-        <v>10836</v>
+        <v>12169</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2020</v>
+        <v>1792</v>
       </c>
       <c r="C5" t="n">
-        <v>10227</v>
+        <v>11097</v>
       </c>
       <c r="D5" t="n">
-        <v>4694</v>
+        <v>5520</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1020</v>
+        <v>923</v>
       </c>
       <c r="C6" t="n">
-        <v>8351</v>
+        <v>8140</v>
       </c>
       <c r="D6" t="n">
-        <v>1419</v>
+        <v>1729</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>292</v>
+        <v>272</v>
       </c>
       <c r="C7" t="n">
-        <v>4696</v>
+        <v>4190</v>
       </c>
       <c r="D7" t="n">
-        <v>606</v>
+        <v>659</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C8" t="n">
-        <v>1938</v>
+        <v>1732</v>
       </c>
       <c r="D8" t="n">
-        <v>385</v>
+        <v>391</v>
       </c>
     </row>
     <row r="9">
@@ -3055,10 +3055,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C9" t="n">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="D9" t="n">
         <v>292</v>
@@ -3072,7 +3072,7 @@
         <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="D10" t="n">
         <v>170</v>
@@ -3089,7 +3089,7 @@
         <v>126</v>
       </c>
       <c r="D11" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12">
@@ -3100,7 +3100,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D12" t="n">
         <v>98</v>
@@ -3114,7 +3114,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D13" t="n">
         <v>60</v>
@@ -3128,7 +3128,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D14" t="n">
         <v>46</v>
@@ -3142,7 +3142,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D15" t="n">
         <v>33</v>
@@ -3156,7 +3156,7 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D16" t="n">
         <v>20</v>
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2383</v>
+        <v>1460</v>
       </c>
       <c r="C2" t="n">
-        <v>4093</v>
+        <v>3761</v>
       </c>
       <c r="D2" t="n">
-        <v>9636</v>
+        <v>10230</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2822</v>
+        <v>2028</v>
       </c>
       <c r="C3" t="n">
-        <v>6130</v>
+        <v>5444</v>
       </c>
       <c r="D3" t="n">
-        <v>12209</v>
+        <v>13552</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2821</v>
+        <v>2374</v>
       </c>
       <c r="C4" t="n">
-        <v>7949</v>
+        <v>8246</v>
       </c>
       <c r="D4" t="n">
-        <v>10873</v>
+        <v>12338</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2205</v>
+        <v>1939</v>
       </c>
       <c r="C5" t="n">
-        <v>9973</v>
+        <v>10670</v>
       </c>
       <c r="D5" t="n">
-        <v>5290</v>
+        <v>6043</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1156</v>
+        <v>1043</v>
       </c>
       <c r="C6" t="n">
-        <v>9230</v>
+        <v>9311</v>
       </c>
       <c r="D6" t="n">
-        <v>1681</v>
+        <v>2033</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>259</v>
+        <v>242</v>
       </c>
       <c r="C7" t="n">
-        <v>5804</v>
+        <v>5327</v>
       </c>
       <c r="D7" t="n">
-        <v>678</v>
+        <v>745</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C8" t="n">
-        <v>2495</v>
+        <v>2233</v>
       </c>
       <c r="D8" t="n">
-        <v>390</v>
+        <v>396</v>
       </c>
     </row>
     <row r="9">
@@ -3369,7 +3369,7 @@
         <v>14</v>
       </c>
       <c r="C9" t="n">
-        <v>567</v>
+        <v>561</v>
       </c>
       <c r="D9" t="n">
         <v>289</v>
@@ -3383,7 +3383,7 @@
         <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D10" t="n">
         <v>174</v>
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D11" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12">
@@ -3411,7 +3411,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D12" t="n">
         <v>91</v>
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D13" t="n">
         <v>61</v>
@@ -3439,7 +3439,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D14" t="n">
         <v>36</v>
@@ -3453,7 +3453,7 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D15" t="n">
         <v>19</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2961</v>
+        <v>2477</v>
       </c>
       <c r="C2" t="n">
-        <v>6322</v>
+        <v>6726</v>
       </c>
       <c r="D2" t="n">
-        <v>11542</v>
+        <v>20484</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2259</v>
+        <v>1554</v>
       </c>
       <c r="C3" t="n">
-        <v>4814</v>
+        <v>4317</v>
       </c>
       <c r="D3" t="n">
-        <v>11158</v>
+        <v>12334</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2451</v>
+        <v>1965</v>
       </c>
       <c r="C4" t="n">
-        <v>7067</v>
+        <v>6971</v>
       </c>
       <c r="D4" t="n">
-        <v>10722</v>
+        <v>12126</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2191</v>
+        <v>1916</v>
       </c>
       <c r="C5" t="n">
-        <v>9007</v>
+        <v>9540</v>
       </c>
       <c r="D5" t="n">
-        <v>5825</v>
+        <v>6644</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1381</v>
+        <v>1214</v>
       </c>
       <c r="C6" t="n">
-        <v>9421</v>
+        <v>9721</v>
       </c>
       <c r="D6" t="n">
-        <v>2059</v>
+        <v>2469</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>461</v>
+        <v>422</v>
       </c>
       <c r="C7" t="n">
-        <v>6976</v>
+        <v>6691</v>
       </c>
       <c r="D7" t="n">
-        <v>789</v>
+        <v>868</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="C8" t="n">
-        <v>3564</v>
+        <v>3254</v>
       </c>
       <c r="D8" t="n">
-        <v>417</v>
+        <v>429</v>
       </c>
     </row>
     <row r="9">
@@ -3680,10 +3680,10 @@
         <v>19</v>
       </c>
       <c r="C9" t="n">
-        <v>1158</v>
+        <v>1052</v>
       </c>
       <c r="D9" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="10">
@@ -3694,7 +3694,7 @@
         <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D10" t="n">
         <v>181</v>
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D12" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13">
@@ -3736,7 +3736,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D13" t="n">
         <v>62</v>
@@ -3750,7 +3750,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D14" t="n">
         <v>36</v>
@@ -3764,7 +3764,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D15" t="n">
         <v>18</v>
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6432</v>
+        <v>6193</v>
       </c>
       <c r="C2" t="n">
-        <v>5896</v>
+        <v>7670</v>
       </c>
       <c r="D2" t="n">
-        <v>3107</v>
+        <v>10711</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2188</v>
+        <v>1829</v>
       </c>
       <c r="C2" t="n">
-        <v>3793</v>
+        <v>4036</v>
       </c>
       <c r="D2" t="n">
-        <v>8587</v>
+        <v>15403</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2949</v>
+        <v>2152</v>
       </c>
       <c r="C3" t="n">
-        <v>5698</v>
+        <v>5333</v>
       </c>
       <c r="D3" t="n">
-        <v>12181</v>
+        <v>13755</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3277</v>
+        <v>2774</v>
       </c>
       <c r="C4" t="n">
-        <v>9998</v>
+        <v>10145</v>
       </c>
       <c r="D4" t="n">
-        <v>10923</v>
+        <v>12368</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1276</v>
+        <v>1121</v>
       </c>
       <c r="C5" t="n">
-        <v>13283</v>
+        <v>13768</v>
       </c>
       <c r="D5" t="n">
-        <v>5167</v>
+        <v>5953</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>425</v>
+        <v>389</v>
       </c>
       <c r="C6" t="n">
-        <v>8406</v>
+        <v>8176</v>
       </c>
       <c r="D6" t="n">
-        <v>1669</v>
+        <v>1934</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C7" t="n">
-        <v>3492</v>
+        <v>3188</v>
       </c>
       <c r="D7" t="n">
-        <v>501</v>
+        <v>522</v>
       </c>
     </row>
     <row r="8">
@@ -4288,10 +4288,10 @@
         <v>17</v>
       </c>
       <c r="C8" t="n">
-        <v>1134</v>
+        <v>1030</v>
       </c>
       <c r="D8" t="n">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="9">
@@ -4302,7 +4302,7 @@
         <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D9" t="n">
         <v>177</v>
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D10" t="n">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D11" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="12">
@@ -4344,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D12" t="n">
         <v>60</v>
@@ -4358,7 +4358,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D13" t="n">
         <v>35</v>
@@ -4372,7 +4372,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D14" t="n">
         <v>17</v>
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7674</v>
+        <v>6754</v>
       </c>
       <c r="C2" t="n">
-        <v>8622</v>
+        <v>8158</v>
       </c>
       <c r="D2" t="n">
-        <v>9615</v>
+        <v>22420</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2732</v>
+        <v>2631</v>
       </c>
       <c r="C3" t="n">
-        <v>3018</v>
+        <v>3865</v>
       </c>
       <c r="D3" t="n">
-        <v>1186</v>
+        <v>2438</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D4" t="n">
         <v>1538</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C5" t="n">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C6" t="n">
         <v>459</v>
       </c>
       <c r="D6" t="n">
-        <v>808</v>
+        <v>816</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>538</v>
       </c>
     </row>
     <row r="8">
@@ -4655,7 +4655,7 @@
         <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D12" t="n">
         <v>199</v>
@@ -4666,10 +4666,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D13" t="n">
         <v>170</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5069</v>
+        <v>4584</v>
       </c>
       <c r="C2" t="n">
-        <v>8532</v>
+        <v>5573</v>
       </c>
       <c r="D2" t="n">
-        <v>16945</v>
+        <v>30963</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4271</v>
+        <v>3854</v>
       </c>
       <c r="C3" t="n">
-        <v>5377</v>
+        <v>5428</v>
       </c>
       <c r="D3" t="n">
-        <v>2514</v>
+        <v>5615</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1220</v>
+        <v>1177</v>
       </c>
       <c r="C4" t="n">
-        <v>1840</v>
+        <v>2309</v>
       </c>
       <c r="D4" t="n">
-        <v>1420</v>
+        <v>1672</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="D5" t="n">
-        <v>1186</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="D6" t="n">
-        <v>864</v>
+        <v>859</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C7" t="n">
         <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>584</v>
       </c>
     </row>
     <row r="8">
@@ -4913,7 +4913,7 @@
         <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="9">
@@ -4921,10 +4921,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C9" t="n">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D9" t="n">
         <v>363</v>
@@ -4935,7 +4935,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C10" t="n">
         <v>192</v>
@@ -4949,10 +4949,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D11" t="n">
         <v>270</v>
@@ -4966,7 +4966,7 @@
         <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D12" t="n">
         <v>206</v>
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C13" t="n">
         <v>103</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="15">
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
         <v>74</v>
@@ -5025,7 +5025,7 @@
         <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5036,10 +5036,10 @@
         <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="18">
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4928</v>
+        <v>5337</v>
       </c>
       <c r="C2" t="n">
-        <v>11499</v>
+        <v>6861</v>
       </c>
       <c r="D2" t="n">
-        <v>22288</v>
+        <v>31137</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3842</v>
+        <v>3471</v>
       </c>
       <c r="C3" t="n">
-        <v>6143</v>
+        <v>4774</v>
       </c>
       <c r="D3" t="n">
-        <v>4641</v>
+        <v>9266</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2323</v>
+        <v>2140</v>
       </c>
       <c r="C4" t="n">
-        <v>3805</v>
+        <v>3975</v>
       </c>
       <c r="D4" t="n">
-        <v>1586</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>561</v>
+        <v>533</v>
       </c>
       <c r="C5" t="n">
-        <v>1099</v>
+        <v>1359</v>
       </c>
       <c r="D5" t="n">
-        <v>1181</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C6" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D6" t="n">
-        <v>910</v>
+        <v>908</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="D7" t="n">
-        <v>625</v>
+        <v>626</v>
       </c>
     </row>
     <row r="8">
@@ -5221,10 +5221,10 @@
         <v>125</v>
       </c>
       <c r="C8" t="n">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="D8" t="n">
-        <v>462</v>
+        <v>454</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C9" t="n">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D9" t="n">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="10">
@@ -5246,10 +5246,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C10" t="n">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D10" t="n">
         <v>346</v>
@@ -5260,10 +5260,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C11" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D11" t="n">
         <v>280</v>
@@ -5277,10 +5277,10 @@
         <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D12" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="13">
@@ -5288,7 +5288,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C13" t="n">
         <v>116</v>
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
         <v>77</v>
       </c>
       <c r="D15" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16">
@@ -5333,10 +5333,10 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17">
@@ -5347,10 +5347,10 @@
         <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5406,7 +5406,7 @@
         <v>122</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5063</v>
+        <v>4889</v>
       </c>
       <c r="C2" t="n">
-        <v>13207</v>
+        <v>13238</v>
       </c>
       <c r="D2" t="n">
-        <v>23889</v>
+        <v>25272</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3587</v>
+        <v>3560</v>
       </c>
       <c r="C3" t="n">
-        <v>7746</v>
+        <v>5081</v>
       </c>
       <c r="D3" t="n">
-        <v>6996</v>
+        <v>11938</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2627</v>
+        <v>2363</v>
       </c>
       <c r="C4" t="n">
-        <v>4982</v>
+        <v>4276</v>
       </c>
       <c r="D4" t="n">
-        <v>2095</v>
+        <v>3562</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1180</v>
+        <v>1101</v>
       </c>
       <c r="C5" t="n">
-        <v>2468</v>
+        <v>2686</v>
       </c>
       <c r="D5" t="n">
-        <v>1203</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>306</v>
+        <v>291</v>
       </c>
       <c r="C6" t="n">
-        <v>704</v>
+        <v>827</v>
       </c>
       <c r="D6" t="n">
-        <v>944</v>
+        <v>952</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="D7" t="n">
-        <v>659</v>
+        <v>666</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C8" t="n">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="D8" t="n">
-        <v>484</v>
+        <v>471</v>
       </c>
     </row>
     <row r="9">
@@ -5546,10 +5546,10 @@
         <v>97</v>
       </c>
       <c r="C9" t="n">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="D9" t="n">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C10" t="n">
         <v>233</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>342</v>
       </c>
     </row>
     <row r="11">
@@ -5571,10 +5571,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C11" t="n">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D11" t="n">
         <v>286</v>
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C12" t="n">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D12" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="13">
@@ -5602,7 +5602,7 @@
         <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D13" t="n">
         <v>176</v>
@@ -5613,10 +5613,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D14" t="n">
         <v>149</v>
@@ -5630,10 +5630,10 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D15" t="n">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16">
@@ -5644,10 +5644,10 @@
         <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5672,7 +5672,7 @@
         <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
         <v>60</v>
@@ -5717,7 +5717,7 @@
         <v>137</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6886</v>
+        <v>5327</v>
       </c>
       <c r="C2" t="n">
-        <v>14496</v>
+        <v>10802</v>
       </c>
       <c r="D2" t="n">
-        <v>33044</v>
+        <v>25952</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3132</v>
+        <v>3048</v>
       </c>
       <c r="C3" t="n">
-        <v>8631</v>
+        <v>7515</v>
       </c>
       <c r="D3" t="n">
-        <v>8533</v>
+        <v>12348</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1932</v>
+        <v>1814</v>
       </c>
       <c r="C4" t="n">
-        <v>5329</v>
+        <v>3822</v>
       </c>
       <c r="D4" t="n">
-        <v>2553</v>
+        <v>4348</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>984</v>
+        <v>897</v>
       </c>
       <c r="C5" t="n">
-        <v>2757</v>
+        <v>2562</v>
       </c>
       <c r="D5" t="n">
-        <v>1060</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>348</v>
+        <v>327</v>
       </c>
       <c r="C6" t="n">
-        <v>1056</v>
+        <v>1175</v>
       </c>
       <c r="D6" t="n">
-        <v>752</v>
+        <v>780</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C7" t="n">
-        <v>336</v>
+        <v>368</v>
       </c>
       <c r="D7" t="n">
-        <v>512</v>
+        <v>517</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C8" t="n">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="D8" t="n">
-        <v>364</v>
+        <v>357</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="D9" t="n">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>233</v>
       </c>
     </row>
     <row r="11">
@@ -5888,7 +5888,7 @@
         <v>114</v>
       </c>
       <c r="D11" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="12">
@@ -5902,7 +5902,7 @@
         <v>92</v>
       </c>
       <c r="D12" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="13">
@@ -5910,10 +5910,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D13" t="n">
         <v>117</v>
@@ -5941,10 +5941,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="16">
@@ -5983,7 +5983,7 @@
         <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -6025,10 +6025,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5280</v>
+        <v>4505</v>
       </c>
       <c r="C2" t="n">
-        <v>7534</v>
+        <v>10234</v>
       </c>
       <c r="D2" t="n">
-        <v>36210</v>
+        <v>27147</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4145</v>
+        <v>3462</v>
       </c>
       <c r="C3" t="n">
-        <v>10338</v>
+        <v>8099</v>
       </c>
       <c r="D3" t="n">
-        <v>12022</v>
+        <v>13724</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2210</v>
+        <v>2123</v>
       </c>
       <c r="C4" t="n">
-        <v>7132</v>
+        <v>5940</v>
       </c>
       <c r="D4" t="n">
-        <v>3680</v>
+        <v>5828</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1286</v>
+        <v>1195</v>
       </c>
       <c r="C5" t="n">
-        <v>4205</v>
+        <v>3209</v>
       </c>
       <c r="D5" t="n">
-        <v>1304</v>
+        <v>1894</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>615</v>
+        <v>566</v>
       </c>
       <c r="C6" t="n">
-        <v>2006</v>
+        <v>1946</v>
       </c>
       <c r="D6" t="n">
-        <v>800</v>
+        <v>884</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="C7" t="n">
-        <v>738</v>
+        <v>818</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>555</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C8" t="n">
-        <v>282</v>
+        <v>301</v>
       </c>
       <c r="D8" t="n">
-        <v>387</v>
+        <v>383</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C9" t="n">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D9" t="n">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="10">
@@ -6182,10 +6182,10 @@
         <v>33</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>234</v>
       </c>
     </row>
     <row r="11">
@@ -6196,7 +6196,7 @@
         <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D11" t="n">
         <v>199</v>
@@ -6210,7 +6210,7 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D12" t="n">
         <v>153</v>
@@ -6221,10 +6221,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D13" t="n">
         <v>119</v>
@@ -6235,10 +6235,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D14" t="n">
         <v>98</v>
@@ -6255,7 +6255,7 @@
         <v>49</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -6336,10 +6336,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4348</v>
+        <v>4634</v>
       </c>
       <c r="C2" t="n">
-        <v>4376</v>
+        <v>11506</v>
       </c>
       <c r="D2" t="n">
-        <v>28432</v>
+        <v>29496</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3863</v>
+        <v>3263</v>
       </c>
       <c r="C3" t="n">
-        <v>7703</v>
+        <v>8009</v>
       </c>
       <c r="D3" t="n">
-        <v>14852</v>
+        <v>14798</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2711</v>
+        <v>2392</v>
       </c>
       <c r="C4" t="n">
-        <v>8737</v>
+        <v>6940</v>
       </c>
       <c r="D4" t="n">
-        <v>5054</v>
+        <v>7035</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1519</v>
+        <v>1439</v>
       </c>
       <c r="C5" t="n">
-        <v>5622</v>
+        <v>4610</v>
       </c>
       <c r="D5" t="n">
-        <v>1697</v>
+        <v>2553</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>858</v>
+        <v>794</v>
       </c>
       <c r="C6" t="n">
-        <v>3123</v>
+        <v>2578</v>
       </c>
       <c r="D6" t="n">
-        <v>868</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>351</v>
+        <v>326</v>
       </c>
       <c r="C7" t="n">
-        <v>1383</v>
+        <v>1384</v>
       </c>
       <c r="D7" t="n">
-        <v>585</v>
+        <v>607</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="C8" t="n">
-        <v>502</v>
+        <v>559</v>
       </c>
       <c r="D8" t="n">
-        <v>409</v>
+        <v>403</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C9" t="n">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c r="D9" t="n">
-        <v>293</v>
+        <v>297</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C10" t="n">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D10" t="n">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="11">
@@ -6535,10 +6535,10 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -6566,7 +6566,7 @@
         <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -6622,7 +6622,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -6647,10 +6647,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_population_iteration_80_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_80_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4788</v>
+        <v>7102</v>
       </c>
       <c r="C2" t="n">
-        <v>14581</v>
+        <v>7949</v>
       </c>
       <c r="D2" t="n">
-        <v>28254</v>
+        <v>28542</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3188</v>
+        <v>4130</v>
       </c>
       <c r="C3" t="n">
-        <v>8569</v>
+        <v>6997</v>
       </c>
       <c r="D3" t="n">
-        <v>15896</v>
+        <v>17220</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2405</v>
+        <v>3057</v>
       </c>
       <c r="C4" t="n">
-        <v>7262</v>
+        <v>6095</v>
       </c>
       <c r="D4" t="n">
-        <v>8162</v>
+        <v>8400</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1640</v>
+        <v>2054</v>
       </c>
       <c r="C5" t="n">
-        <v>5654</v>
+        <v>4707</v>
       </c>
       <c r="D5" t="n">
-        <v>3182</v>
+        <v>3054</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>985</v>
+        <v>1256</v>
       </c>
       <c r="C6" t="n">
-        <v>3482</v>
+        <v>2926</v>
       </c>
       <c r="D6" t="n">
-        <v>1270</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>480</v>
+        <v>608</v>
       </c>
       <c r="C7" t="n">
-        <v>1945</v>
+        <v>1759</v>
       </c>
       <c r="D7" t="n">
-        <v>662</v>
+        <v>644</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>179</v>
+        <v>226</v>
       </c>
       <c r="C8" t="n">
-        <v>925</v>
+        <v>771</v>
       </c>
       <c r="D8" t="n">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="C9" t="n">
-        <v>387</v>
+        <v>317</v>
       </c>
       <c r="D9" t="n">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="D10" t="n">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D12" t="n">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -993,10 +993,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5545</v>
+        <v>7748</v>
       </c>
       <c r="C2" t="n">
-        <v>9621</v>
+        <v>7311</v>
       </c>
       <c r="D2" t="n">
-        <v>28471</v>
+        <v>31218</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3161</v>
+        <v>4440</v>
       </c>
       <c r="C3" t="n">
-        <v>9876</v>
+        <v>6541</v>
       </c>
       <c r="D3" t="n">
-        <v>16435</v>
+        <v>17602</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2356</v>
+        <v>2996</v>
       </c>
       <c r="C4" t="n">
-        <v>7713</v>
+        <v>6392</v>
       </c>
       <c r="D4" t="n">
-        <v>9023</v>
+        <v>9584</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1733</v>
+        <v>2192</v>
       </c>
       <c r="C5" t="n">
-        <v>6192</v>
+        <v>5190</v>
       </c>
       <c r="D5" t="n">
-        <v>3850</v>
+        <v>3752</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1143</v>
+        <v>1452</v>
       </c>
       <c r="C6" t="n">
-        <v>4387</v>
+        <v>3684</v>
       </c>
       <c r="D6" t="n">
-        <v>1516</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>615</v>
+        <v>794</v>
       </c>
       <c r="C7" t="n">
-        <v>2572</v>
+        <v>2244</v>
       </c>
       <c r="D7" t="n">
-        <v>744</v>
+        <v>708</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>266</v>
+        <v>334</v>
       </c>
       <c r="C8" t="n">
-        <v>1344</v>
+        <v>1187</v>
       </c>
       <c r="D8" t="n">
-        <v>453</v>
+        <v>457</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>97</v>
+        <v>118</v>
       </c>
       <c r="C9" t="n">
-        <v>593</v>
+        <v>496</v>
       </c>
       <c r="D9" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="10">
@@ -1203,10 +1203,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C10" t="n">
-        <v>278</v>
+        <v>249</v>
       </c>
       <c r="D10" t="n">
         <v>247</v>
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C11" t="n">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="D12" t="n">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="13">
@@ -1262,10 +1262,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -1307,7 +1307,7 @@
         <v>39</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1318,7 +1318,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6707</v>
+        <v>8649</v>
       </c>
       <c r="C2" t="n">
-        <v>15694</v>
+        <v>7433</v>
       </c>
       <c r="D2" t="n">
-        <v>25578</v>
+        <v>25984</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3320</v>
+        <v>4676</v>
       </c>
       <c r="C3" t="n">
-        <v>8713</v>
+        <v>6089</v>
       </c>
       <c r="D3" t="n">
-        <v>16827</v>
+        <v>18109</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2274</v>
+        <v>3033</v>
       </c>
       <c r="C4" t="n">
-        <v>8371</v>
+        <v>6260</v>
       </c>
       <c r="D4" t="n">
-        <v>9816</v>
+        <v>10355</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1775</v>
+        <v>2255</v>
       </c>
       <c r="C5" t="n">
-        <v>6676</v>
+        <v>5578</v>
       </c>
       <c r="D5" t="n">
-        <v>4391</v>
+        <v>4477</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1246</v>
+        <v>1587</v>
       </c>
       <c r="C6" t="n">
-        <v>5000</v>
+        <v>4208</v>
       </c>
       <c r="D6" t="n">
-        <v>1809</v>
+        <v>1722</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>730</v>
+        <v>941</v>
       </c>
       <c r="C7" t="n">
-        <v>3239</v>
+        <v>2785</v>
       </c>
       <c r="D7" t="n">
-        <v>827</v>
+        <v>802</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>348</v>
+        <v>447</v>
       </c>
       <c r="C8" t="n">
-        <v>1800</v>
+        <v>1590</v>
       </c>
       <c r="D8" t="n">
-        <v>485</v>
+        <v>479</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>137</v>
+        <v>171</v>
       </c>
       <c r="C9" t="n">
-        <v>851</v>
+        <v>741</v>
       </c>
       <c r="D9" t="n">
-        <v>328</v>
+        <v>334</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="C10" t="n">
-        <v>383</v>
+        <v>333</v>
       </c>
       <c r="D10" t="n">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C11" t="n">
-        <v>211</v>
+        <v>201</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13">
@@ -1559,7 +1559,7 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D13" t="n">
         <v>128</v>
@@ -1573,10 +1573,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -1590,7 +1590,7 @@
         <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -1618,7 +1618,7 @@
         <v>41</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1629,7 +1629,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6164</v>
+        <v>8005</v>
       </c>
       <c r="C2" t="n">
-        <v>11048</v>
+        <v>5113</v>
       </c>
       <c r="D2" t="n">
-        <v>21270</v>
+        <v>21656</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3974</v>
+        <v>5492</v>
       </c>
       <c r="C3" t="n">
-        <v>13487</v>
+        <v>9322</v>
       </c>
       <c r="D3" t="n">
-        <v>18455</v>
+        <v>19696</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1640</v>
+        <v>2083</v>
       </c>
       <c r="C4" t="n">
-        <v>10828</v>
+        <v>8720</v>
       </c>
       <c r="D4" t="n">
-        <v>9390</v>
+        <v>9854</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1151</v>
+        <v>1466</v>
       </c>
       <c r="C5" t="n">
-        <v>4900</v>
+        <v>4123</v>
       </c>
       <c r="D5" t="n">
-        <v>2910</v>
+        <v>2890</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>674</v>
+        <v>869</v>
       </c>
       <c r="C6" t="n">
-        <v>3174</v>
+        <v>2729</v>
       </c>
       <c r="D6" t="n">
-        <v>810</v>
+        <v>785</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>321</v>
+        <v>413</v>
       </c>
       <c r="C7" t="n">
-        <v>1764</v>
+        <v>1558</v>
       </c>
       <c r="D7" t="n">
-        <v>475</v>
+        <v>469</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>126</v>
+        <v>158</v>
       </c>
       <c r="C8" t="n">
-        <v>833</v>
+        <v>726</v>
       </c>
       <c r="D8" t="n">
-        <v>321</v>
+        <v>327</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="C9" t="n">
-        <v>375</v>
+        <v>326</v>
       </c>
       <c r="D9" t="n">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C10" t="n">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="D10" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C11" t="n">
         <v>147</v>
       </c>
       <c r="D11" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="12">
@@ -1856,7 +1856,7 @@
         <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D12" t="n">
         <v>125</v>
@@ -1870,10 +1870,10 @@
         <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D13" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14">
@@ -1887,7 +1887,7 @@
         <v>66</v>
       </c>
       <c r="D14" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D15" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="16">
@@ -1915,7 +1915,7 @@
         <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17">
@@ -1926,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D17" t="n">
         <v>38</v>
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D19" t="n">
         <v>15</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3782</v>
+        <v>4936</v>
       </c>
       <c r="C2" t="n">
-        <v>4947</v>
+        <v>2229</v>
       </c>
       <c r="D2" t="n">
-        <v>14523</v>
+        <v>15925</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4191</v>
+        <v>5649</v>
       </c>
       <c r="C3" t="n">
-        <v>11322</v>
+        <v>6739</v>
       </c>
       <c r="D3" t="n">
-        <v>17781</v>
+        <v>19017</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2193</v>
+        <v>2939</v>
       </c>
       <c r="C4" t="n">
-        <v>12088</v>
+        <v>9150</v>
       </c>
       <c r="D4" t="n">
-        <v>10590</v>
+        <v>11066</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1257</v>
+        <v>1604</v>
       </c>
       <c r="C5" t="n">
-        <v>7366</v>
+        <v>6088</v>
       </c>
       <c r="D5" t="n">
-        <v>3623</v>
+        <v>3726</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>788</v>
+        <v>1024</v>
       </c>
       <c r="C6" t="n">
-        <v>3901</v>
+        <v>3337</v>
       </c>
       <c r="D6" t="n">
-        <v>1005</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>298</v>
+        <v>385</v>
       </c>
       <c r="C7" t="n">
-        <v>2278</v>
+        <v>2004</v>
       </c>
       <c r="D7" t="n">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>104</v>
+        <v>130</v>
       </c>
       <c r="C8" t="n">
-        <v>1092</v>
+        <v>959</v>
       </c>
       <c r="D8" t="n">
-        <v>330</v>
+        <v>336</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="C9" t="n">
-        <v>411</v>
+        <v>370</v>
       </c>
       <c r="D9" t="n">
-        <v>257</v>
+        <v>254</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="D10" t="n">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="11">
@@ -2153,10 +2153,10 @@
         <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D11" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="12">
@@ -2167,10 +2167,10 @@
         <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="D12" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="13">
@@ -2184,7 +2184,7 @@
         <v>64</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D14" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="15">
@@ -2212,7 +2212,7 @@
         <v>39</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16">
@@ -2223,7 +2223,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D16" t="n">
         <v>37</v>
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D18" t="n">
         <v>14</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3378</v>
+        <v>6152</v>
       </c>
       <c r="C2" t="n">
-        <v>9692</v>
+        <v>12004</v>
       </c>
       <c r="D2" t="n">
-        <v>16978</v>
+        <v>17179</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3418</v>
+        <v>4498</v>
       </c>
       <c r="C3" t="n">
-        <v>7482</v>
+        <v>4144</v>
       </c>
       <c r="D3" t="n">
-        <v>16313</v>
+        <v>17318</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2569</v>
+        <v>3525</v>
       </c>
       <c r="C4" t="n">
-        <v>11476</v>
+        <v>7802</v>
       </c>
       <c r="D4" t="n">
-        <v>11270</v>
+        <v>12027</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1457</v>
+        <v>1914</v>
       </c>
       <c r="C5" t="n">
-        <v>9414</v>
+        <v>7372</v>
       </c>
       <c r="D5" t="n">
-        <v>4582</v>
+        <v>4740</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>897</v>
+        <v>1162</v>
       </c>
       <c r="C6" t="n">
-        <v>5328</v>
+        <v>4552</v>
       </c>
       <c r="D6" t="n">
-        <v>1368</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="7">
@@ -2405,10 +2405,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>426</v>
+        <v>558</v>
       </c>
       <c r="C7" t="n">
-        <v>2967</v>
+        <v>2564</v>
       </c>
       <c r="D7" t="n">
         <v>578</v>
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>148</v>
+        <v>190</v>
       </c>
       <c r="C8" t="n">
-        <v>1555</v>
+        <v>1387</v>
       </c>
       <c r="D8" t="n">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="C9" t="n">
-        <v>655</v>
+        <v>596</v>
       </c>
       <c r="D9" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>288</v>
+        <v>270</v>
       </c>
       <c r="D10" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11">
@@ -2464,10 +2464,10 @@
         <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="D11" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="12">
@@ -2478,10 +2478,10 @@
         <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D12" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15">
@@ -2520,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D15" t="n">
         <v>48</v>
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D16" t="n">
         <v>36</v>
@@ -2562,7 +2562,7 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D18" t="n">
         <v>13</v>
@@ -2576,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
         <v>6</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2075</v>
+        <v>3684</v>
       </c>
       <c r="C2" t="n">
-        <v>4743</v>
+        <v>5677</v>
       </c>
       <c r="D2" t="n">
-        <v>11993</v>
+        <v>11986</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3294</v>
+        <v>4712</v>
       </c>
       <c r="C3" t="n">
-        <v>7979</v>
+        <v>6602</v>
       </c>
       <c r="D3" t="n">
-        <v>16037</v>
+        <v>16915</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2805</v>
+        <v>3872</v>
       </c>
       <c r="C4" t="n">
-        <v>11150</v>
+        <v>7229</v>
       </c>
       <c r="D4" t="n">
-        <v>11943</v>
+        <v>12741</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1530</v>
+        <v>2009</v>
       </c>
       <c r="C5" t="n">
-        <v>11277</v>
+        <v>8563</v>
       </c>
       <c r="D5" t="n">
-        <v>4688</v>
+        <v>4999</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>741</v>
+        <v>977</v>
       </c>
       <c r="C6" t="n">
-        <v>6092</v>
+        <v>5376</v>
       </c>
       <c r="D6" t="n">
-        <v>1327</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>136</v>
+        <v>175</v>
       </c>
       <c r="C7" t="n">
-        <v>2971</v>
+        <v>2635</v>
       </c>
       <c r="D7" t="n">
-        <v>571</v>
+        <v>577</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="C8" t="n">
-        <v>1083</v>
+        <v>991</v>
       </c>
       <c r="D8" t="n">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>282</v>
+        <v>264</v>
       </c>
       <c r="D9" t="n">
-        <v>281</v>
+        <v>285</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D10" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="11">
@@ -2775,10 +2775,10 @@
         <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D11" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14">
@@ -2817,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D14" t="n">
         <v>47</v>
@@ -2831,7 +2831,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D15" t="n">
         <v>35</v>
@@ -2859,7 +2859,7 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
         <v>12</v>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
         <v>5</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2074</v>
+        <v>4612</v>
       </c>
       <c r="C2" t="n">
-        <v>5887</v>
+        <v>8098</v>
       </c>
       <c r="D2" t="n">
-        <v>11970</v>
+        <v>15126</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2415</v>
+        <v>3667</v>
       </c>
       <c r="C3" t="n">
-        <v>5919</v>
+        <v>5521</v>
       </c>
       <c r="D3" t="n">
-        <v>14621</v>
+        <v>15270</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2639</v>
+        <v>3669</v>
       </c>
       <c r="C4" t="n">
-        <v>9517</v>
+        <v>6789</v>
       </c>
       <c r="D4" t="n">
-        <v>12169</v>
+        <v>12994</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1792</v>
+        <v>2435</v>
       </c>
       <c r="C5" t="n">
-        <v>11097</v>
+        <v>7877</v>
       </c>
       <c r="D5" t="n">
-        <v>5520</v>
+        <v>5961</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>923</v>
+        <v>1243</v>
       </c>
       <c r="C6" t="n">
-        <v>8140</v>
+        <v>6695</v>
       </c>
       <c r="D6" t="n">
-        <v>1729</v>
+        <v>1817</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>272</v>
+        <v>362</v>
       </c>
       <c r="C7" t="n">
-        <v>4190</v>
+        <v>3760</v>
       </c>
       <c r="D7" t="n">
-        <v>659</v>
+        <v>674</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="C8" t="n">
-        <v>1732</v>
+        <v>1590</v>
       </c>
       <c r="D8" t="n">
-        <v>391</v>
+        <v>396</v>
       </c>
     </row>
     <row r="9">
@@ -3055,10 +3055,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C9" t="n">
-        <v>525</v>
+        <v>499</v>
       </c>
       <c r="D9" t="n">
         <v>292</v>
@@ -3072,10 +3072,10 @@
         <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D10" t="n">
-        <v>170</v>
+        <v>174</v>
       </c>
     </row>
     <row r="11">
@@ -3086,7 +3086,7 @@
         <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="D11" t="n">
         <v>134</v>
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14">
@@ -3128,7 +3128,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D14" t="n">
         <v>46</v>
@@ -3142,7 +3142,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D15" t="n">
         <v>33</v>
@@ -3156,7 +3156,7 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D16" t="n">
         <v>20</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1460</v>
+        <v>3365</v>
       </c>
       <c r="C2" t="n">
-        <v>3761</v>
+        <v>4229</v>
       </c>
       <c r="D2" t="n">
-        <v>10230</v>
+        <v>11422</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2028</v>
+        <v>3472</v>
       </c>
       <c r="C3" t="n">
-        <v>5444</v>
+        <v>5977</v>
       </c>
       <c r="D3" t="n">
-        <v>13552</v>
+        <v>14568</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2374</v>
+        <v>3344</v>
       </c>
       <c r="C4" t="n">
-        <v>8246</v>
+        <v>6344</v>
       </c>
       <c r="D4" t="n">
-        <v>12338</v>
+        <v>13007</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1939</v>
+        <v>2667</v>
       </c>
       <c r="C5" t="n">
-        <v>10670</v>
+        <v>7564</v>
       </c>
       <c r="D5" t="n">
-        <v>6043</v>
+        <v>6579</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1043</v>
+        <v>1448</v>
       </c>
       <c r="C6" t="n">
-        <v>9311</v>
+        <v>7330</v>
       </c>
       <c r="D6" t="n">
-        <v>2033</v>
+        <v>2206</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>242</v>
+        <v>324</v>
       </c>
       <c r="C7" t="n">
-        <v>5327</v>
+        <v>4706</v>
       </c>
       <c r="D7" t="n">
-        <v>745</v>
+        <v>754</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="C8" t="n">
-        <v>2233</v>
+        <v>2073</v>
       </c>
       <c r="D8" t="n">
-        <v>396</v>
+        <v>411</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>561</v>
+        <v>574</v>
       </c>
       <c r="D9" t="n">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="D10" t="n">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D12" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13">
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D13" t="n">
         <v>61</v>
@@ -3439,7 +3439,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D14" t="n">
         <v>36</v>
@@ -3453,7 +3453,7 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D15" t="n">
         <v>19</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2477</v>
+        <v>4821</v>
       </c>
       <c r="C2" t="n">
-        <v>6726</v>
+        <v>11924</v>
       </c>
       <c r="D2" t="n">
-        <v>20484</v>
+        <v>16862</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1554</v>
+        <v>2891</v>
       </c>
       <c r="C3" t="n">
-        <v>4317</v>
+        <v>4725</v>
       </c>
       <c r="D3" t="n">
-        <v>12334</v>
+        <v>13397</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1965</v>
+        <v>2944</v>
       </c>
       <c r="C4" t="n">
-        <v>6971</v>
+        <v>6060</v>
       </c>
       <c r="D4" t="n">
-        <v>12126</v>
+        <v>12696</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1916</v>
+        <v>2665</v>
       </c>
       <c r="C5" t="n">
-        <v>9540</v>
+        <v>6926</v>
       </c>
       <c r="D5" t="n">
-        <v>6644</v>
+        <v>7242</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1214</v>
+        <v>1715</v>
       </c>
       <c r="C6" t="n">
-        <v>9721</v>
+        <v>7357</v>
       </c>
       <c r="D6" t="n">
-        <v>2469</v>
+        <v>2723</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>422</v>
+        <v>588</v>
       </c>
       <c r="C7" t="n">
-        <v>6691</v>
+        <v>5655</v>
       </c>
       <c r="D7" t="n">
-        <v>868</v>
+        <v>917</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87</v>
+        <v>117</v>
       </c>
       <c r="C8" t="n">
-        <v>3254</v>
+        <v>2995</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>443</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C9" t="n">
-        <v>1052</v>
+        <v>1049</v>
       </c>
       <c r="D9" t="n">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="10">
@@ -3694,10 +3694,10 @@
         <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>309</v>
+        <v>318</v>
       </c>
       <c r="D10" t="n">
-        <v>181</v>
+        <v>184</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="D11" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13">
@@ -3736,7 +3736,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D13" t="n">
         <v>62</v>
@@ -3750,7 +3750,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D14" t="n">
         <v>36</v>
@@ -3764,7 +3764,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D15" t="n">
         <v>18</v>
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
         <v>7</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6193</v>
+        <v>7959</v>
       </c>
       <c r="C2" t="n">
-        <v>7670</v>
+        <v>4180</v>
       </c>
       <c r="D2" t="n">
-        <v>10711</v>
+        <v>7689</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1829</v>
+        <v>3486</v>
       </c>
       <c r="C2" t="n">
-        <v>4036</v>
+        <v>6963</v>
       </c>
       <c r="D2" t="n">
-        <v>15403</v>
+        <v>12545</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2152</v>
+        <v>3827</v>
       </c>
       <c r="C3" t="n">
-        <v>5333</v>
+        <v>6703</v>
       </c>
       <c r="D3" t="n">
-        <v>13755</v>
+        <v>14658</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2774</v>
+        <v>3943</v>
       </c>
       <c r="C4" t="n">
-        <v>10145</v>
+        <v>8486</v>
       </c>
       <c r="D4" t="n">
-        <v>12368</v>
+        <v>13073</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1121</v>
+        <v>1633</v>
       </c>
       <c r="C5" t="n">
-        <v>13768</v>
+        <v>10228</v>
       </c>
       <c r="D5" t="n">
-        <v>5953</v>
+        <v>6575</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>389</v>
+        <v>543</v>
       </c>
       <c r="C6" t="n">
-        <v>8176</v>
+        <v>6911</v>
       </c>
       <c r="D6" t="n">
-        <v>1934</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>80</v>
+        <v>108</v>
       </c>
       <c r="C7" t="n">
-        <v>3188</v>
+        <v>2935</v>
       </c>
       <c r="D7" t="n">
-        <v>522</v>
+        <v>550</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C8" t="n">
-        <v>1030</v>
+        <v>1028</v>
       </c>
       <c r="D8" t="n">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="9">
@@ -4302,10 +4302,10 @@
         <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="D9" t="n">
-        <v>177</v>
+        <v>180</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="D10" t="n">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="D11" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="12">
@@ -4344,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D12" t="n">
         <v>60</v>
@@ -4358,7 +4358,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D13" t="n">
         <v>35</v>
@@ -4372,7 +4372,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
         <v>17</v>
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D15" t="n">
         <v>6</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6754</v>
+        <v>9051</v>
       </c>
       <c r="C2" t="n">
-        <v>8158</v>
+        <v>8569</v>
       </c>
       <c r="D2" t="n">
-        <v>22420</v>
+        <v>14940</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2631</v>
+        <v>3380</v>
       </c>
       <c r="C3" t="n">
-        <v>3865</v>
+        <v>2106</v>
       </c>
       <c r="D3" t="n">
-        <v>2438</v>
+        <v>1931</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D4" t="n">
         <v>1538</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C5" t="n">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C6" t="n">
         <v>459</v>
       </c>
       <c r="D6" t="n">
-        <v>816</v>
+        <v>808</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>546</v>
       </c>
     </row>
     <row r="8">
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4584</v>
+        <v>5677</v>
       </c>
       <c r="C2" t="n">
-        <v>5573</v>
+        <v>6360</v>
       </c>
       <c r="D2" t="n">
-        <v>30963</v>
+        <v>28711</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3854</v>
+        <v>5103</v>
       </c>
       <c r="C3" t="n">
-        <v>5428</v>
+        <v>4970</v>
       </c>
       <c r="D3" t="n">
-        <v>5615</v>
+        <v>3974</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1177</v>
+        <v>1502</v>
       </c>
       <c r="C4" t="n">
-        <v>2309</v>
+        <v>1277</v>
       </c>
       <c r="D4" t="n">
-        <v>1672</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="D5" t="n">
-        <v>1198</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="6">
@@ -4882,10 +4882,10 @@
         <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="D6" t="n">
-        <v>859</v>
+        <v>864</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C7" t="n">
         <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>589</v>
       </c>
     </row>
     <row r="8">
@@ -4913,7 +4913,7 @@
         <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="9">
@@ -4921,7 +4921,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C9" t="n">
         <v>232</v>
@@ -4935,10 +4935,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D10" t="n">
         <v>352</v>
@@ -4952,7 +4952,7 @@
         <v>43</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D11" t="n">
         <v>270</v>
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C15" t="n">
         <v>74</v>
@@ -5022,10 +5022,10 @@
         <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17">
@@ -5036,10 +5036,10 @@
         <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5337</v>
+        <v>5757</v>
       </c>
       <c r="C2" t="n">
-        <v>6861</v>
+        <v>7015</v>
       </c>
       <c r="D2" t="n">
-        <v>31137</v>
+        <v>29031</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3471</v>
+        <v>4442</v>
       </c>
       <c r="C3" t="n">
-        <v>4774</v>
+        <v>4958</v>
       </c>
       <c r="D3" t="n">
-        <v>9266</v>
+        <v>7645</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2140</v>
+        <v>2808</v>
       </c>
       <c r="C4" t="n">
-        <v>3975</v>
+        <v>3342</v>
       </c>
       <c r="D4" t="n">
-        <v>2378</v>
+        <v>1983</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>533</v>
+        <v>663</v>
       </c>
       <c r="C5" t="n">
-        <v>1359</v>
+        <v>793</v>
       </c>
       <c r="D5" t="n">
-        <v>1236</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="6">
@@ -5193,10 +5193,10 @@
         <v>148</v>
       </c>
       <c r="C6" t="n">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D6" t="n">
-        <v>908</v>
+        <v>910</v>
       </c>
     </row>
     <row r="7">
@@ -5207,10 +5207,10 @@
         <v>158</v>
       </c>
       <c r="C7" t="n">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="D7" t="n">
-        <v>626</v>
+        <v>631</v>
       </c>
     </row>
     <row r="8">
@@ -5221,10 +5221,10 @@
         <v>125</v>
       </c>
       <c r="C8" t="n">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="D8" t="n">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="9">
@@ -5238,7 +5238,7 @@
         <v>268</v>
       </c>
       <c r="D9" t="n">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="10">
@@ -5246,10 +5246,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D10" t="n">
         <v>346</v>
@@ -5263,7 +5263,7 @@
         <v>47</v>
       </c>
       <c r="C11" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D11" t="n">
         <v>280</v>
@@ -5277,7 +5277,7 @@
         <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D12" t="n">
         <v>213</v>
@@ -5316,10 +5316,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D15" t="n">
         <v>120</v>
@@ -5336,7 +5336,7 @@
         <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5350,7 +5350,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18">
@@ -5375,7 +5375,7 @@
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D19" t="n">
         <v>41</v>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4889</v>
+        <v>5959</v>
       </c>
       <c r="C2" t="n">
-        <v>13238</v>
+        <v>4805</v>
       </c>
       <c r="D2" t="n">
-        <v>25272</v>
+        <v>33533</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3560</v>
+        <v>4162</v>
       </c>
       <c r="C3" t="n">
-        <v>5081</v>
+        <v>5236</v>
       </c>
       <c r="D3" t="n">
-        <v>11938</v>
+        <v>10357</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2363</v>
+        <v>3056</v>
       </c>
       <c r="C4" t="n">
-        <v>4276</v>
+        <v>4141</v>
       </c>
       <c r="D4" t="n">
-        <v>3562</v>
+        <v>2955</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1101</v>
+        <v>1419</v>
       </c>
       <c r="C5" t="n">
-        <v>2686</v>
+        <v>2097</v>
       </c>
       <c r="D5" t="n">
-        <v>1383</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>291</v>
+        <v>348</v>
       </c>
       <c r="C6" t="n">
-        <v>827</v>
+        <v>542</v>
       </c>
       <c r="D6" t="n">
-        <v>952</v>
+        <v>948</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C7" t="n">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="D7" t="n">
-        <v>666</v>
+        <v>664</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C8" t="n">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D8" t="n">
-        <v>471</v>
+        <v>480</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C9" t="n">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D9" t="n">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="10">
@@ -5557,10 +5557,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C10" t="n">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="D10" t="n">
         <v>342</v>
@@ -5574,7 +5574,7 @@
         <v>50</v>
       </c>
       <c r="C11" t="n">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D11" t="n">
         <v>286</v>
@@ -5588,7 +5588,7 @@
         <v>34</v>
       </c>
       <c r="C12" t="n">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D12" t="n">
         <v>217</v>
@@ -5602,7 +5602,7 @@
         <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D13" t="n">
         <v>176</v>
@@ -5619,7 +5619,7 @@
         <v>100</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5630,10 +5630,10 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16">
@@ -5647,7 +5647,7 @@
         <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17">
@@ -5661,7 +5661,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18">
@@ -5700,7 +5700,7 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D20" t="n">
         <v>24</v>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5327</v>
+        <v>7119</v>
       </c>
       <c r="C2" t="n">
-        <v>10802</v>
+        <v>12816</v>
       </c>
       <c r="D2" t="n">
-        <v>25952</v>
+        <v>36686</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3048</v>
+        <v>3663</v>
       </c>
       <c r="C3" t="n">
-        <v>7515</v>
+        <v>4109</v>
       </c>
       <c r="D3" t="n">
-        <v>12348</v>
+        <v>12371</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1814</v>
+        <v>2244</v>
       </c>
       <c r="C4" t="n">
-        <v>3822</v>
+        <v>3886</v>
       </c>
       <c r="D4" t="n">
-        <v>4348</v>
+        <v>3680</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>897</v>
+        <v>1159</v>
       </c>
       <c r="C5" t="n">
-        <v>2562</v>
+        <v>2307</v>
       </c>
       <c r="D5" t="n">
-        <v>1380</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>327</v>
+        <v>412</v>
       </c>
       <c r="C6" t="n">
-        <v>1175</v>
+        <v>878</v>
       </c>
       <c r="D6" t="n">
-        <v>780</v>
+        <v>766</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="C7" t="n">
-        <v>368</v>
+        <v>285</v>
       </c>
       <c r="D7" t="n">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D8" t="n">
-        <v>357</v>
+        <v>362</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="D9" t="n">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D10" t="n">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="11">
@@ -5885,7 +5885,7 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D11" t="n">
         <v>195</v>
@@ -5913,7 +5913,7 @@
         <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D13" t="n">
         <v>117</v>
@@ -5941,10 +5941,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D15" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -5958,7 +5958,7 @@
         <v>38</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -6011,7 +6011,7 @@
         <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>15</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4505</v>
+        <v>6045</v>
       </c>
       <c r="C2" t="n">
-        <v>10234</v>
+        <v>7087</v>
       </c>
       <c r="D2" t="n">
-        <v>27147</v>
+        <v>27274</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3462</v>
+        <v>4459</v>
       </c>
       <c r="C3" t="n">
-        <v>8099</v>
+        <v>7918</v>
       </c>
       <c r="D3" t="n">
-        <v>13724</v>
+        <v>15545</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2123</v>
+        <v>2559</v>
       </c>
       <c r="C4" t="n">
-        <v>5940</v>
+        <v>3940</v>
       </c>
       <c r="D4" t="n">
-        <v>5828</v>
+        <v>5284</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1195</v>
+        <v>1521</v>
       </c>
       <c r="C5" t="n">
-        <v>3209</v>
+        <v>3183</v>
       </c>
       <c r="D5" t="n">
-        <v>1894</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>566</v>
+        <v>726</v>
       </c>
       <c r="C6" t="n">
-        <v>1946</v>
+        <v>1676</v>
       </c>
       <c r="D6" t="n">
-        <v>884</v>
+        <v>845</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>189</v>
+        <v>231</v>
       </c>
       <c r="C7" t="n">
-        <v>818</v>
+        <v>616</v>
       </c>
       <c r="D7" t="n">
-        <v>555</v>
+        <v>552</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="C8" t="n">
-        <v>301</v>
+        <v>255</v>
       </c>
       <c r="D8" t="n">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
     <row r="9">
@@ -6165,10 +6165,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C9" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D9" t="n">
         <v>284</v>
@@ -6185,7 +6185,7 @@
         <v>172</v>
       </c>
       <c r="D10" t="n">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="11">
@@ -6210,7 +6210,7 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D12" t="n">
         <v>153</v>
@@ -6224,7 +6224,7 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D13" t="n">
         <v>119</v>
@@ -6255,7 +6255,7 @@
         <v>49</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -6269,7 +6269,7 @@
         <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -6280,7 +6280,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D17" t="n">
         <v>51</v>
@@ -6322,7 +6322,7 @@
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4634</v>
+        <v>5912</v>
       </c>
       <c r="C2" t="n">
-        <v>11506</v>
+        <v>9609</v>
       </c>
       <c r="D2" t="n">
-        <v>29496</v>
+        <v>30469</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3263</v>
+        <v>4296</v>
       </c>
       <c r="C3" t="n">
-        <v>8009</v>
+        <v>6480</v>
       </c>
       <c r="D3" t="n">
-        <v>14798</v>
+        <v>16302</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2392</v>
+        <v>2979</v>
       </c>
       <c r="C4" t="n">
-        <v>6940</v>
+        <v>6072</v>
       </c>
       <c r="D4" t="n">
-        <v>7035</v>
+        <v>7093</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1439</v>
+        <v>1797</v>
       </c>
       <c r="C5" t="n">
-        <v>4610</v>
+        <v>3493</v>
       </c>
       <c r="D5" t="n">
-        <v>2553</v>
+        <v>2295</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>794</v>
+        <v>1008</v>
       </c>
       <c r="C6" t="n">
-        <v>2578</v>
+        <v>2452</v>
       </c>
       <c r="D6" t="n">
-        <v>1037</v>
+        <v>971</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>326</v>
+        <v>418</v>
       </c>
       <c r="C7" t="n">
-        <v>1384</v>
+        <v>1166</v>
       </c>
       <c r="D7" t="n">
-        <v>607</v>
+        <v>598</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>111</v>
+        <v>130</v>
       </c>
       <c r="C8" t="n">
-        <v>559</v>
+        <v>435</v>
       </c>
       <c r="D8" t="n">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C9" t="n">
-        <v>253</v>
+        <v>229</v>
       </c>
       <c r="D9" t="n">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="10">
@@ -6493,10 +6493,10 @@
         <v>35</v>
       </c>
       <c r="C10" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D10" t="n">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12">
@@ -6532,10 +6532,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D13" t="n">
         <v>121</v>
@@ -6549,7 +6549,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
         <v>99</v>
@@ -6566,7 +6566,7 @@
         <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -6577,10 +6577,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -6591,10 +6591,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -6633,7 +6633,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>

--- a/output/yearly_population_iteration_80_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_80_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7102</v>
+        <v>1386</v>
       </c>
       <c r="C2" t="n">
-        <v>7949</v>
+        <v>2701</v>
       </c>
       <c r="D2" t="n">
-        <v>28542</v>
+        <v>15575</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4130</v>
+        <v>2310</v>
       </c>
       <c r="C3" t="n">
-        <v>6997</v>
+        <v>6796</v>
       </c>
       <c r="D3" t="n">
-        <v>17220</v>
+        <v>13449</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3057</v>
+        <v>1610</v>
       </c>
       <c r="C4" t="n">
-        <v>6095</v>
+        <v>10432</v>
       </c>
       <c r="D4" t="n">
-        <v>8400</v>
+        <v>5912</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2054</v>
+        <v>865</v>
       </c>
       <c r="C5" t="n">
-        <v>4707</v>
+        <v>6365</v>
       </c>
       <c r="D5" t="n">
-        <v>3054</v>
+        <v>1857</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1256</v>
+        <v>360</v>
       </c>
       <c r="C6" t="n">
-        <v>2926</v>
+        <v>1822</v>
       </c>
       <c r="D6" t="n">
-        <v>1173</v>
+        <v>740</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>608</v>
+        <v>106</v>
       </c>
       <c r="C7" t="n">
-        <v>1759</v>
+        <v>545</v>
       </c>
       <c r="D7" t="n">
-        <v>644</v>
+        <v>483</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>226</v>
+        <v>73</v>
       </c>
       <c r="C8" t="n">
-        <v>771</v>
+        <v>327</v>
       </c>
       <c r="D8" t="n">
-        <v>431</v>
+        <v>372</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>76</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>317</v>
+        <v>281</v>
       </c>
       <c r="D9" t="n">
-        <v>307</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="C10" t="n">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>265</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="D11" t="n">
-        <v>202</v>
+        <v>212</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>127</v>
+        <v>110</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>174</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>98</v>
+        <v>77</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>138</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15">
@@ -968,7 +968,7 @@
         <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>141</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7748</v>
+        <v>1165</v>
       </c>
       <c r="C2" t="n">
-        <v>7311</v>
+        <v>8772</v>
       </c>
       <c r="D2" t="n">
-        <v>31218</v>
+        <v>15301</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4440</v>
+        <v>1603</v>
       </c>
       <c r="C3" t="n">
-        <v>6541</v>
+        <v>4080</v>
       </c>
       <c r="D3" t="n">
-        <v>17602</v>
+        <v>12825</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2996</v>
+        <v>1681</v>
       </c>
       <c r="C4" t="n">
-        <v>6392</v>
+        <v>8360</v>
       </c>
       <c r="D4" t="n">
-        <v>9584</v>
+        <v>7107</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2192</v>
+        <v>1063</v>
       </c>
       <c r="C5" t="n">
-        <v>5190</v>
+        <v>8301</v>
       </c>
       <c r="D5" t="n">
-        <v>3752</v>
+        <v>2501</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1452</v>
+        <v>524</v>
       </c>
       <c r="C6" t="n">
-        <v>3684</v>
+        <v>4044</v>
       </c>
       <c r="D6" t="n">
-        <v>1446</v>
+        <v>912</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>794</v>
+        <v>186</v>
       </c>
       <c r="C7" t="n">
-        <v>2244</v>
+        <v>1150</v>
       </c>
       <c r="D7" t="n">
-        <v>708</v>
+        <v>523</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>334</v>
+        <v>80</v>
       </c>
       <c r="C8" t="n">
-        <v>1187</v>
+        <v>426</v>
       </c>
       <c r="D8" t="n">
-        <v>457</v>
+        <v>383</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>118</v>
+        <v>55</v>
       </c>
       <c r="C9" t="n">
-        <v>496</v>
+        <v>305</v>
       </c>
       <c r="D9" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="C10" t="n">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="D10" t="n">
-        <v>247</v>
+        <v>271</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="D11" t="n">
-        <v>205</v>
+        <v>217</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="D12" t="n">
-        <v>163</v>
+        <v>176</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>141</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>94</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>83</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>96</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>77</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8649</v>
+        <v>629</v>
       </c>
       <c r="C2" t="n">
-        <v>7433</v>
+        <v>3764</v>
       </c>
       <c r="D2" t="n">
-        <v>25984</v>
+        <v>10465</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4676</v>
+        <v>1427</v>
       </c>
       <c r="C3" t="n">
-        <v>6089</v>
+        <v>5687</v>
       </c>
       <c r="D3" t="n">
-        <v>18109</v>
+        <v>12793</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3033</v>
+        <v>1835</v>
       </c>
       <c r="C4" t="n">
-        <v>6260</v>
+        <v>7386</v>
       </c>
       <c r="D4" t="n">
-        <v>10355</v>
+        <v>7835</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2255</v>
+        <v>1081</v>
       </c>
       <c r="C5" t="n">
-        <v>5578</v>
+        <v>9378</v>
       </c>
       <c r="D5" t="n">
-        <v>4477</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1587</v>
+        <v>399</v>
       </c>
       <c r="C6" t="n">
-        <v>4208</v>
+        <v>5035</v>
       </c>
       <c r="D6" t="n">
-        <v>1722</v>
+        <v>931</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>941</v>
+        <v>73</v>
       </c>
       <c r="C7" t="n">
-        <v>2785</v>
+        <v>1082</v>
       </c>
       <c r="D7" t="n">
-        <v>802</v>
+        <v>552</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>447</v>
+        <v>50</v>
       </c>
       <c r="C8" t="n">
-        <v>1590</v>
+        <v>445</v>
       </c>
       <c r="D8" t="n">
-        <v>479</v>
+        <v>435</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>171</v>
+        <v>26</v>
       </c>
       <c r="C9" t="n">
-        <v>741</v>
+        <v>236</v>
       </c>
       <c r="D9" t="n">
-        <v>334</v>
+        <v>363</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>333</v>
+        <v>187</v>
       </c>
       <c r="D10" t="n">
-        <v>250</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>201</v>
+        <v>128</v>
       </c>
       <c r="D11" t="n">
-        <v>207</v>
+        <v>172</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>150</v>
+        <v>84</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>68</v>
       </c>
       <c r="D13" t="n">
-        <v>128</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>89</v>
+        <v>63</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>83</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C17" t="n">
-        <v>41</v>
+        <v>94</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8005</v>
+        <v>1006</v>
       </c>
       <c r="C2" t="n">
-        <v>5113</v>
+        <v>10835</v>
       </c>
       <c r="D2" t="n">
-        <v>21656</v>
+        <v>11495</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5492</v>
+        <v>914</v>
       </c>
       <c r="C3" t="n">
-        <v>9322</v>
+        <v>4192</v>
       </c>
       <c r="D3" t="n">
-        <v>19696</v>
+        <v>11577</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2083</v>
+        <v>1476</v>
       </c>
       <c r="C4" t="n">
-        <v>8720</v>
+        <v>6438</v>
       </c>
       <c r="D4" t="n">
-        <v>9854</v>
+        <v>8453</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1466</v>
+        <v>1258</v>
       </c>
       <c r="C5" t="n">
-        <v>4123</v>
+        <v>8316</v>
       </c>
       <c r="D5" t="n">
-        <v>2890</v>
+        <v>3581</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>869</v>
+        <v>607</v>
       </c>
       <c r="C6" t="n">
-        <v>2729</v>
+        <v>6994</v>
       </c>
       <c r="D6" t="n">
-        <v>785</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>413</v>
+        <v>161</v>
       </c>
       <c r="C7" t="n">
-        <v>1558</v>
+        <v>2807</v>
       </c>
       <c r="D7" t="n">
-        <v>469</v>
+        <v>603</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>158</v>
+        <v>54</v>
       </c>
       <c r="C8" t="n">
-        <v>726</v>
+        <v>703</v>
       </c>
       <c r="D8" t="n">
-        <v>327</v>
+        <v>448</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>58</v>
+        <v>29</v>
       </c>
       <c r="C9" t="n">
-        <v>326</v>
+        <v>318</v>
       </c>
       <c r="D9" t="n">
-        <v>245</v>
+        <v>369</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>196</v>
+        <v>208</v>
       </c>
       <c r="D10" t="n">
-        <v>202</v>
+        <v>225</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="C11" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D11" t="n">
-        <v>160</v>
+        <v>178</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>112</v>
+        <v>96</v>
       </c>
       <c r="D12" t="n">
-        <v>125</v>
+        <v>141</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>81</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
+        <v>66</v>
+      </c>
+      <c r="D15" t="n">
         <v>49</v>
-      </c>
-      <c r="D15" t="n">
-        <v>61</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>91</v>
       </c>
       <c r="D16" t="n">
-        <v>49</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33</v>
+        <v>100</v>
       </c>
       <c r="D17" t="n">
-        <v>38</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4936</v>
+        <v>577</v>
       </c>
       <c r="C2" t="n">
-        <v>2229</v>
+        <v>4771</v>
       </c>
       <c r="D2" t="n">
-        <v>15925</v>
+        <v>8374</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5649</v>
+        <v>827</v>
       </c>
       <c r="C3" t="n">
-        <v>6739</v>
+        <v>6420</v>
       </c>
       <c r="D3" t="n">
-        <v>19017</v>
+        <v>10918</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2939</v>
+        <v>1195</v>
       </c>
       <c r="C4" t="n">
-        <v>9150</v>
+        <v>5497</v>
       </c>
       <c r="D4" t="n">
-        <v>11066</v>
+        <v>8727</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1604</v>
+        <v>1303</v>
       </c>
       <c r="C5" t="n">
-        <v>6088</v>
+        <v>7643</v>
       </c>
       <c r="D5" t="n">
-        <v>3726</v>
+        <v>4148</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1024</v>
+        <v>737</v>
       </c>
       <c r="C6" t="n">
-        <v>3337</v>
+        <v>7808</v>
       </c>
       <c r="D6" t="n">
-        <v>1000</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>385</v>
+        <v>170</v>
       </c>
       <c r="C7" t="n">
-        <v>2004</v>
+        <v>4147</v>
       </c>
       <c r="D7" t="n">
-        <v>518</v>
+        <v>669</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>130</v>
+        <v>51</v>
       </c>
       <c r="C8" t="n">
-        <v>959</v>
+        <v>1162</v>
       </c>
       <c r="D8" t="n">
-        <v>336</v>
+        <v>471</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="C9" t="n">
+        <v>399</v>
+      </c>
+      <c r="D9" t="n">
         <v>370</v>
-      </c>
-      <c r="D9" t="n">
-        <v>254</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="D10" t="n">
-        <v>210</v>
+        <v>231</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="D11" t="n">
-        <v>166</v>
+        <v>186</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="D12" t="n">
-        <v>131</v>
+        <v>135</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>39</v>
+        <v>89</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>32</v>
+        <v>98</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6152</v>
+        <v>1756</v>
       </c>
       <c r="C2" t="n">
-        <v>12004</v>
+        <v>10756</v>
       </c>
       <c r="D2" t="n">
-        <v>17179</v>
+        <v>12645</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4498</v>
+        <v>614</v>
       </c>
       <c r="C3" t="n">
-        <v>4144</v>
+        <v>5075</v>
       </c>
       <c r="D3" t="n">
-        <v>17318</v>
+        <v>9876</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3525</v>
+        <v>916</v>
       </c>
       <c r="C4" t="n">
-        <v>7802</v>
+        <v>5807</v>
       </c>
       <c r="D4" t="n">
-        <v>12027</v>
+        <v>8798</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1914</v>
+        <v>1171</v>
       </c>
       <c r="C5" t="n">
-        <v>7372</v>
+        <v>6536</v>
       </c>
       <c r="D5" t="n">
-        <v>4740</v>
+        <v>4641</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1162</v>
+        <v>879</v>
       </c>
       <c r="C6" t="n">
-        <v>4552</v>
+        <v>7742</v>
       </c>
       <c r="D6" t="n">
-        <v>1379</v>
+        <v>1801</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>558</v>
+        <v>324</v>
       </c>
       <c r="C7" t="n">
-        <v>2564</v>
+        <v>5616</v>
       </c>
       <c r="D7" t="n">
-        <v>578</v>
+        <v>766</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>190</v>
+        <v>79</v>
       </c>
       <c r="C8" t="n">
-        <v>1387</v>
+        <v>2313</v>
       </c>
       <c r="D8" t="n">
-        <v>355</v>
+        <v>496</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>62</v>
+        <v>29</v>
       </c>
       <c r="C9" t="n">
-        <v>596</v>
+        <v>671</v>
       </c>
       <c r="D9" t="n">
-        <v>263</v>
+        <v>377</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C10" t="n">
-        <v>270</v>
+        <v>284</v>
       </c>
       <c r="D10" t="n">
-        <v>212</v>
+        <v>242</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="D11" t="n">
-        <v>169</v>
+        <v>189</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D12" t="n">
-        <v>133</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="D13" t="n">
-        <v>103</v>
+        <v>94</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>92</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>34</v>
+        <v>97</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3684</v>
+        <v>1208</v>
       </c>
       <c r="C2" t="n">
-        <v>5677</v>
+        <v>5852</v>
       </c>
       <c r="D2" t="n">
-        <v>11986</v>
+        <v>9206</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4712</v>
+        <v>992</v>
       </c>
       <c r="C3" t="n">
-        <v>6602</v>
+        <v>6943</v>
       </c>
       <c r="D3" t="n">
-        <v>16915</v>
+        <v>10898</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3872</v>
+        <v>1535</v>
       </c>
       <c r="C4" t="n">
-        <v>7229</v>
+        <v>8076</v>
       </c>
       <c r="D4" t="n">
-        <v>12741</v>
+        <v>9008</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2009</v>
+        <v>866</v>
       </c>
       <c r="C5" t="n">
-        <v>8563</v>
+        <v>10297</v>
       </c>
       <c r="D5" t="n">
-        <v>4999</v>
+        <v>4250</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>977</v>
+        <v>299</v>
       </c>
       <c r="C6" t="n">
-        <v>5376</v>
+        <v>7248</v>
       </c>
       <c r="D6" t="n">
-        <v>1344</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>175</v>
+        <v>72</v>
       </c>
       <c r="C7" t="n">
-        <v>2635</v>
+        <v>2266</v>
       </c>
       <c r="D7" t="n">
-        <v>577</v>
+        <v>591</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>57</v>
+        <v>26</v>
       </c>
       <c r="C8" t="n">
-        <v>991</v>
+        <v>657</v>
       </c>
       <c r="D8" t="n">
-        <v>375</v>
+        <v>369</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C9" t="n">
-        <v>264</v>
+        <v>278</v>
       </c>
       <c r="D9" t="n">
-        <v>285</v>
+        <v>237</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="D10" t="n">
-        <v>165</v>
+        <v>185</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D11" t="n">
-        <v>130</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D12" t="n">
-        <v>100</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="D13" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>90</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>33</v>
+        <v>95</v>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4612</v>
+        <v>608</v>
       </c>
       <c r="C2" t="n">
-        <v>8098</v>
+        <v>2981</v>
       </c>
       <c r="D2" t="n">
-        <v>15126</v>
+        <v>6766</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3667</v>
+        <v>913</v>
       </c>
       <c r="C3" t="n">
-        <v>5521</v>
+        <v>5679</v>
       </c>
       <c r="D3" t="n">
-        <v>15270</v>
+        <v>9902</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3669</v>
+        <v>1072</v>
       </c>
       <c r="C4" t="n">
-        <v>6789</v>
+        <v>7125</v>
       </c>
       <c r="D4" t="n">
-        <v>12994</v>
+        <v>8666</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2435</v>
+        <v>809</v>
       </c>
       <c r="C5" t="n">
-        <v>7877</v>
+        <v>8150</v>
       </c>
       <c r="D5" t="n">
-        <v>5961</v>
+        <v>4363</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1243</v>
+        <v>294</v>
       </c>
       <c r="C6" t="n">
-        <v>6695</v>
+        <v>7047</v>
       </c>
       <c r="D6" t="n">
-        <v>1817</v>
+        <v>1621</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>362</v>
+        <v>61</v>
       </c>
       <c r="C7" t="n">
-        <v>3760</v>
+        <v>3062</v>
       </c>
       <c r="D7" t="n">
-        <v>674</v>
+        <v>570</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>79</v>
+        <v>13</v>
       </c>
       <c r="C8" t="n">
-        <v>1590</v>
+        <v>791</v>
       </c>
       <c r="D8" t="n">
-        <v>396</v>
+        <v>320</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>499</v>
+        <v>255</v>
       </c>
       <c r="D9" t="n">
-        <v>292</v>
+        <v>186</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>209</v>
+        <v>122</v>
       </c>
       <c r="D10" t="n">
-        <v>174</v>
+        <v>141</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>129</v>
+        <v>74</v>
       </c>
       <c r="D11" t="n">
-        <v>134</v>
+        <v>99</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>81</v>
+        <v>52</v>
       </c>
       <c r="D12" t="n">
-        <v>101</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D13" t="n">
-        <v>59</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3365</v>
+        <v>724</v>
       </c>
       <c r="C2" t="n">
-        <v>4229</v>
+        <v>8597</v>
       </c>
       <c r="D2" t="n">
-        <v>11422</v>
+        <v>13618</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3472</v>
+        <v>648</v>
       </c>
       <c r="C3" t="n">
-        <v>5977</v>
+        <v>3758</v>
       </c>
       <c r="D3" t="n">
-        <v>14568</v>
+        <v>8728</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3344</v>
+        <v>878</v>
       </c>
       <c r="C4" t="n">
-        <v>6344</v>
+        <v>6199</v>
       </c>
       <c r="D4" t="n">
-        <v>13007</v>
+        <v>8628</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2667</v>
+        <v>833</v>
       </c>
       <c r="C5" t="n">
-        <v>7564</v>
+        <v>7527</v>
       </c>
       <c r="D5" t="n">
-        <v>6579</v>
+        <v>4973</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1448</v>
+        <v>474</v>
       </c>
       <c r="C6" t="n">
-        <v>7330</v>
+        <v>7512</v>
       </c>
       <c r="D6" t="n">
-        <v>2206</v>
+        <v>2046</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>324</v>
+        <v>139</v>
       </c>
       <c r="C7" t="n">
-        <v>4706</v>
+        <v>5004</v>
       </c>
       <c r="D7" t="n">
-        <v>754</v>
+        <v>728</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="C8" t="n">
-        <v>2073</v>
+        <v>1822</v>
       </c>
       <c r="D8" t="n">
-        <v>411</v>
+        <v>353</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C9" t="n">
-        <v>574</v>
+        <v>483</v>
       </c>
       <c r="D9" t="n">
-        <v>288</v>
+        <v>202</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>214</v>
+        <v>175</v>
       </c>
       <c r="D10" t="n">
-        <v>177</v>
+        <v>146</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>128</v>
+        <v>92</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>102</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>9</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4821</v>
+        <v>629</v>
       </c>
       <c r="C2" t="n">
-        <v>11924</v>
+        <v>9557</v>
       </c>
       <c r="D2" t="n">
-        <v>16862</v>
+        <v>14398</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2891</v>
+        <v>563</v>
       </c>
       <c r="C3" t="n">
-        <v>4725</v>
+        <v>5275</v>
       </c>
       <c r="D3" t="n">
-        <v>13397</v>
+        <v>8806</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2944</v>
+        <v>673</v>
       </c>
       <c r="C4" t="n">
-        <v>6060</v>
+        <v>4874</v>
       </c>
       <c r="D4" t="n">
-        <v>12696</v>
+        <v>8299</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2665</v>
+        <v>776</v>
       </c>
       <c r="C5" t="n">
-        <v>6926</v>
+        <v>6745</v>
       </c>
       <c r="D5" t="n">
-        <v>7242</v>
+        <v>5418</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1715</v>
+        <v>576</v>
       </c>
       <c r="C6" t="n">
-        <v>7357</v>
+        <v>7371</v>
       </c>
       <c r="D6" t="n">
-        <v>2723</v>
+        <v>2468</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>588</v>
+        <v>245</v>
       </c>
       <c r="C7" t="n">
-        <v>5655</v>
+        <v>6132</v>
       </c>
       <c r="D7" t="n">
-        <v>917</v>
+        <v>907</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>117</v>
+        <v>62</v>
       </c>
       <c r="C8" t="n">
-        <v>2995</v>
+        <v>3193</v>
       </c>
       <c r="D8" t="n">
-        <v>443</v>
+        <v>404</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="C9" t="n">
-        <v>1049</v>
+        <v>1033</v>
       </c>
       <c r="D9" t="n">
-        <v>297</v>
+        <v>220</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>318</v>
+        <v>295</v>
       </c>
       <c r="D10" t="n">
-        <v>184</v>
+        <v>150</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>151</v>
+        <v>122</v>
       </c>
       <c r="D11" t="n">
-        <v>139</v>
+        <v>106</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="D12" t="n">
-        <v>94</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>22</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>65</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7959</v>
+        <v>6582</v>
       </c>
       <c r="C2" t="n">
-        <v>4180</v>
+        <v>3527</v>
       </c>
       <c r="D2" t="n">
-        <v>7689</v>
+        <v>7625</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>843</v>
+        <v>855</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="C4" t="n">
-        <v>313</v>
+        <v>344</v>
       </c>
       <c r="D4" t="n">
-        <v>1805</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>249</v>
+        <v>314</v>
       </c>
       <c r="C5" t="n">
-        <v>515</v>
+        <v>586</v>
       </c>
       <c r="D5" t="n">
-        <v>1038</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>182</v>
+        <v>255</v>
       </c>
       <c r="C6" t="n">
-        <v>395</v>
+        <v>488</v>
       </c>
       <c r="D6" t="n">
-        <v>777</v>
+        <v>898</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>129</v>
+        <v>202</v>
       </c>
       <c r="C7" t="n">
-        <v>293</v>
+        <v>388</v>
       </c>
       <c r="D7" t="n">
-        <v>496</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>171</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>420</v>
+        <v>531</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="C9" t="n">
-        <v>187</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>349</v>
+        <v>445</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>265</v>
       </c>
       <c r="D10" t="n">
-        <v>362</v>
+        <v>485</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>215</v>
       </c>
       <c r="D11" t="n">
-        <v>245</v>
+        <v>327</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="D12" t="n">
-        <v>196</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="C13" t="n">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="D13" t="n">
-        <v>168</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="D14" t="n">
-        <v>145</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="D15" t="n">
-        <v>117</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="D16" t="n">
-        <v>97</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C17" t="n">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="D17" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C18" t="n">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="D18" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -4156,10 +4156,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C21" t="n">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3486</v>
+        <v>495</v>
       </c>
       <c r="C2" t="n">
-        <v>6963</v>
+        <v>16600</v>
       </c>
       <c r="D2" t="n">
-        <v>12545</v>
+        <v>19108</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3827</v>
+        <v>488</v>
       </c>
       <c r="C3" t="n">
-        <v>6703</v>
+        <v>6251</v>
       </c>
       <c r="D3" t="n">
-        <v>14658</v>
+        <v>9028</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3943</v>
+        <v>543</v>
       </c>
       <c r="C4" t="n">
-        <v>8486</v>
+        <v>4949</v>
       </c>
       <c r="D4" t="n">
-        <v>13073</v>
+        <v>8040</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1633</v>
+        <v>678</v>
       </c>
       <c r="C5" t="n">
-        <v>10228</v>
+        <v>5749</v>
       </c>
       <c r="D5" t="n">
-        <v>6575</v>
+        <v>5668</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>543</v>
+        <v>602</v>
       </c>
       <c r="C6" t="n">
-        <v>6911</v>
+        <v>7046</v>
       </c>
       <c r="D6" t="n">
-        <v>2089</v>
+        <v>2808</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>108</v>
+        <v>334</v>
       </c>
       <c r="C7" t="n">
-        <v>2935</v>
+        <v>6627</v>
       </c>
       <c r="D7" t="n">
-        <v>550</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>21</v>
+        <v>111</v>
       </c>
       <c r="C8" t="n">
-        <v>1028</v>
+        <v>4283</v>
       </c>
       <c r="D8" t="n">
-        <v>291</v>
+        <v>460</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="C9" t="n">
-        <v>311</v>
+        <v>1836</v>
       </c>
       <c r="D9" t="n">
-        <v>180</v>
+        <v>241</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>147</v>
+        <v>552</v>
       </c>
       <c r="D10" t="n">
-        <v>136</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>87</v>
+        <v>181</v>
       </c>
       <c r="D11" t="n">
-        <v>92</v>
+        <v>110</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>49</v>
+        <v>86</v>
       </c>
       <c r="D12" t="n">
-        <v>60</v>
+        <v>69</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="D13" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9051</v>
+        <v>5934</v>
       </c>
       <c r="C2" t="n">
-        <v>8569</v>
+        <v>14085</v>
       </c>
       <c r="D2" t="n">
-        <v>14940</v>
+        <v>17618</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3380</v>
+        <v>2172</v>
       </c>
       <c r="C3" t="n">
-        <v>2106</v>
+        <v>1392</v>
       </c>
       <c r="D3" t="n">
-        <v>1931</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C4" t="n">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="D4" t="n">
-        <v>1538</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>191</v>
+        <v>148</v>
       </c>
       <c r="C5" t="n">
-        <v>384</v>
+        <v>334</v>
       </c>
       <c r="D5" t="n">
-        <v>1161</v>
+        <v>986</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>202</v>
+        <v>143</v>
       </c>
       <c r="C6" t="n">
-        <v>459</v>
+        <v>360</v>
       </c>
       <c r="D6" t="n">
-        <v>808</v>
+        <v>712</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>277</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>260</v>
+        <v>206</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="D9" t="n">
-        <v>354</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>151</v>
       </c>
       <c r="D10" t="n">
-        <v>356</v>
+        <v>324</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>129</v>
       </c>
       <c r="D11" t="n">
-        <v>261</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>199</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C21" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5677</v>
+        <v>3086</v>
       </c>
       <c r="C2" t="n">
-        <v>6360</v>
+        <v>10626</v>
       </c>
       <c r="D2" t="n">
-        <v>28711</v>
+        <v>22845</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5103</v>
+        <v>3414</v>
       </c>
       <c r="C3" t="n">
-        <v>4970</v>
+        <v>7791</v>
       </c>
       <c r="D3" t="n">
-        <v>3974</v>
+        <v>4345</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1502</v>
+        <v>1028</v>
       </c>
       <c r="C4" t="n">
-        <v>1277</v>
+        <v>916</v>
       </c>
       <c r="D4" t="n">
-        <v>1570</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C5" t="n">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="D5" t="n">
-        <v>1186</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>185</v>
+        <v>135</v>
       </c>
       <c r="C6" t="n">
-        <v>411</v>
+        <v>340</v>
       </c>
       <c r="D6" t="n">
-        <v>864</v>
+        <v>756</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>114</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>324</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>509</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>83</v>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>247</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>188</v>
       </c>
       <c r="D9" t="n">
-        <v>363</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="C10" t="n">
-        <v>190</v>
+        <v>160</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>318</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>139</v>
       </c>
       <c r="D11" t="n">
-        <v>270</v>
+        <v>244</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>206</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5757</v>
+        <v>2782</v>
       </c>
       <c r="C2" t="n">
-        <v>7015</v>
+        <v>11025</v>
       </c>
       <c r="D2" t="n">
-        <v>29031</v>
+        <v>25431</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4442</v>
+        <v>2679</v>
       </c>
       <c r="C3" t="n">
-        <v>4958</v>
+        <v>8112</v>
       </c>
       <c r="D3" t="n">
-        <v>7645</v>
+        <v>7133</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2808</v>
+        <v>1950</v>
       </c>
       <c r="C4" t="n">
-        <v>3342</v>
+        <v>4988</v>
       </c>
       <c r="D4" t="n">
-        <v>1983</v>
+        <v>1987</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>663</v>
+        <v>485</v>
       </c>
       <c r="C5" t="n">
-        <v>793</v>
+        <v>610</v>
       </c>
       <c r="D5" t="n">
-        <v>1208</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>148</v>
+        <v>110</v>
       </c>
       <c r="C6" t="n">
-        <v>305</v>
+        <v>261</v>
       </c>
       <c r="D6" t="n">
-        <v>910</v>
+        <v>799</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>116</v>
       </c>
       <c r="C7" t="n">
-        <v>405</v>
+        <v>332</v>
       </c>
       <c r="D7" t="n">
-        <v>631</v>
+        <v>549</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>91</v>
       </c>
       <c r="C8" t="n">
-        <v>358</v>
+        <v>287</v>
       </c>
       <c r="D8" t="n">
-        <v>456</v>
+        <v>407</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>90</v>
+        <v>67</v>
       </c>
       <c r="C9" t="n">
-        <v>268</v>
+        <v>217</v>
       </c>
       <c r="D9" t="n">
-        <v>372</v>
+        <v>329</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="C10" t="n">
-        <v>209</v>
+        <v>173</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>314</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="C11" t="n">
-        <v>175</v>
+        <v>148</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
-        <v>148</v>
+        <v>124</v>
       </c>
       <c r="D12" t="n">
-        <v>213</v>
+        <v>194</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>173</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C21" t="n">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5959</v>
+        <v>2050</v>
       </c>
       <c r="C2" t="n">
-        <v>4805</v>
+        <v>9046</v>
       </c>
       <c r="D2" t="n">
-        <v>33533</v>
+        <v>20704</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4162</v>
+        <v>2254</v>
       </c>
       <c r="C3" t="n">
-        <v>5236</v>
+        <v>8396</v>
       </c>
       <c r="D3" t="n">
-        <v>10357</v>
+        <v>9547</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3056</v>
+        <v>1998</v>
       </c>
       <c r="C4" t="n">
-        <v>4141</v>
+        <v>6653</v>
       </c>
       <c r="D4" t="n">
-        <v>2955</v>
+        <v>2914</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1419</v>
+        <v>1022</v>
       </c>
       <c r="C5" t="n">
-        <v>2097</v>
+        <v>2992</v>
       </c>
       <c r="D5" t="n">
-        <v>1293</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>348</v>
+        <v>263</v>
       </c>
       <c r="C6" t="n">
-        <v>542</v>
+        <v>442</v>
       </c>
       <c r="D6" t="n">
-        <v>948</v>
+        <v>838</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>143</v>
+        <v>106</v>
       </c>
       <c r="C7" t="n">
-        <v>354</v>
+        <v>294</v>
       </c>
       <c r="D7" t="n">
-        <v>664</v>
+        <v>587</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>130</v>
+        <v>94</v>
       </c>
       <c r="C8" t="n">
-        <v>380</v>
+        <v>309</v>
       </c>
       <c r="D8" t="n">
-        <v>480</v>
+        <v>422</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="C9" t="n">
-        <v>306</v>
+        <v>248</v>
       </c>
       <c r="D9" t="n">
-        <v>381</v>
+        <v>338</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>71</v>
+        <v>52</v>
       </c>
       <c r="C10" t="n">
-        <v>235</v>
+        <v>193</v>
       </c>
       <c r="D10" t="n">
-        <v>342</v>
+        <v>313</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C11" t="n">
-        <v>189</v>
+        <v>159</v>
       </c>
       <c r="D11" t="n">
-        <v>286</v>
+        <v>254</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>157</v>
+        <v>134</v>
       </c>
       <c r="D12" t="n">
-        <v>217</v>
+        <v>200</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>128</v>
+        <v>108</v>
       </c>
       <c r="D13" t="n">
-        <v>176</v>
+        <v>161</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7119</v>
+        <v>2856</v>
       </c>
       <c r="C2" t="n">
-        <v>12816</v>
+        <v>8565</v>
       </c>
       <c r="D2" t="n">
-        <v>36686</v>
+        <v>25724</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3663</v>
+        <v>1791</v>
       </c>
       <c r="C3" t="n">
-        <v>4109</v>
+        <v>7607</v>
       </c>
       <c r="D3" t="n">
-        <v>12371</v>
+        <v>10570</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2244</v>
+        <v>1819</v>
       </c>
       <c r="C4" t="n">
-        <v>3886</v>
+        <v>7371</v>
       </c>
       <c r="D4" t="n">
-        <v>3680</v>
+        <v>4035</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1159</v>
+        <v>1304</v>
       </c>
       <c r="C5" t="n">
-        <v>2307</v>
+        <v>4827</v>
       </c>
       <c r="D5" t="n">
-        <v>1238</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>412</v>
+        <v>549</v>
       </c>
       <c r="C6" t="n">
-        <v>878</v>
+        <v>1710</v>
       </c>
       <c r="D6" t="n">
-        <v>766</v>
+        <v>888</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>106</v>
+        <v>158</v>
       </c>
       <c r="C7" t="n">
-        <v>285</v>
+        <v>366</v>
       </c>
       <c r="D7" t="n">
-        <v>516</v>
+        <v>622</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>93</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>301</v>
       </c>
       <c r="D8" t="n">
-        <v>362</v>
+        <v>439</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="C9" t="n">
-        <v>199</v>
+        <v>272</v>
       </c>
       <c r="D9" t="n">
-        <v>271</v>
+        <v>347</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="C10" t="n">
-        <v>149</v>
+        <v>217</v>
       </c>
       <c r="D10" t="n">
-        <v>235</v>
+        <v>313</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="C11" t="n">
-        <v>115</v>
+        <v>173</v>
       </c>
       <c r="D11" t="n">
-        <v>195</v>
+        <v>257</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>143</v>
       </c>
       <c r="D12" t="n">
-        <v>147</v>
+        <v>205</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>117</v>
       </c>
       <c r="D13" t="n">
-        <v>117</v>
+        <v>162</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>93</v>
       </c>
       <c r="D14" t="n">
-        <v>96</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>76</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6022,10 +6022,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>75</v>
+        <v>132</v>
       </c>
       <c r="D21" t="n">
         <v>5</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6045</v>
+        <v>2938</v>
       </c>
       <c r="C2" t="n">
-        <v>7087</v>
+        <v>6939</v>
       </c>
       <c r="D2" t="n">
-        <v>27274</v>
+        <v>25412</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4459</v>
+        <v>1852</v>
       </c>
       <c r="C3" t="n">
-        <v>7918</v>
+        <v>7068</v>
       </c>
       <c r="D3" t="n">
-        <v>15545</v>
+        <v>12126</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2559</v>
+        <v>1570</v>
       </c>
       <c r="C4" t="n">
-        <v>3940</v>
+        <v>7335</v>
       </c>
       <c r="D4" t="n">
-        <v>5284</v>
+        <v>4940</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1521</v>
+        <v>1358</v>
       </c>
       <c r="C5" t="n">
-        <v>3183</v>
+        <v>5947</v>
       </c>
       <c r="D5" t="n">
-        <v>1692</v>
+        <v>1824</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>726</v>
+        <v>791</v>
       </c>
       <c r="C6" t="n">
-        <v>1676</v>
+        <v>3112</v>
       </c>
       <c r="D6" t="n">
-        <v>845</v>
+        <v>953</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>231</v>
+        <v>289</v>
       </c>
       <c r="C7" t="n">
-        <v>616</v>
+        <v>984</v>
       </c>
       <c r="D7" t="n">
-        <v>552</v>
+        <v>657</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>75</v>
+        <v>109</v>
       </c>
       <c r="C8" t="n">
-        <v>255</v>
+        <v>329</v>
       </c>
       <c r="D8" t="n">
-        <v>386</v>
+        <v>457</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>76</v>
       </c>
       <c r="C9" t="n">
-        <v>210</v>
+        <v>281</v>
       </c>
       <c r="D9" t="n">
-        <v>284</v>
+        <v>356</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>57</v>
       </c>
       <c r="C10" t="n">
-        <v>172</v>
+        <v>239</v>
       </c>
       <c r="D10" t="n">
-        <v>236</v>
+        <v>314</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>190</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>258</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="C12" t="n">
-        <v>102</v>
+        <v>154</v>
       </c>
       <c r="D12" t="n">
-        <v>153</v>
+        <v>209</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>81</v>
+        <v>124</v>
       </c>
       <c r="D13" t="n">
-        <v>119</v>
+        <v>163</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>63</v>
+        <v>101</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>137</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>81</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>69</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6333,10 +6333,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>83</v>
+        <v>144</v>
       </c>
       <c r="D21" t="n">
         <v>6</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5912</v>
+        <v>2665</v>
       </c>
       <c r="C2" t="n">
-        <v>9609</v>
+        <v>4385</v>
       </c>
       <c r="D2" t="n">
-        <v>30469</v>
+        <v>20155</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4296</v>
+        <v>2599</v>
       </c>
       <c r="C3" t="n">
-        <v>6480</v>
+        <v>10486</v>
       </c>
       <c r="D3" t="n">
-        <v>16302</v>
+        <v>13237</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2979</v>
+        <v>1254</v>
       </c>
       <c r="C4" t="n">
-        <v>6072</v>
+        <v>10215</v>
       </c>
       <c r="D4" t="n">
-        <v>7093</v>
+        <v>4545</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1797</v>
+        <v>730</v>
       </c>
       <c r="C5" t="n">
-        <v>3493</v>
+        <v>3049</v>
       </c>
       <c r="D5" t="n">
-        <v>2295</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1008</v>
+        <v>267</v>
       </c>
       <c r="C6" t="n">
-        <v>2452</v>
+        <v>964</v>
       </c>
       <c r="D6" t="n">
-        <v>971</v>
+        <v>643</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>418</v>
+        <v>100</v>
       </c>
       <c r="C7" t="n">
-        <v>1166</v>
+        <v>322</v>
       </c>
       <c r="D7" t="n">
-        <v>598</v>
+        <v>447</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>130</v>
+        <v>70</v>
       </c>
       <c r="C8" t="n">
-        <v>435</v>
+        <v>275</v>
       </c>
       <c r="D8" t="n">
-        <v>405</v>
+        <v>348</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="D9" t="n">
-        <v>298</v>
+        <v>307</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C10" t="n">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="D10" t="n">
-        <v>238</v>
+        <v>252</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D11" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="D12" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>121</v>
+        <v>134</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>111</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18">
@@ -6602,10 +6602,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>144</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
